--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -435,31 +435,68 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_RpNumber}
+</t>
+  </si>
+  <si>
+    <t>Rp番号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:drugNumber</t>
+  </si>
+  <si>
+    <t>drugNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DrugNumber}
+</t>
+  </si>
+  <si>
+    <t>薬剤番号</t>
+  </si>
+  <si>
+    <t>薬剤番号を表現する拡張</t>
+  </si>
+  <si>
+    <t>MedicationRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -470,6 +507,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -477,9 +517,6 @@
   </si>
   <si>
     <t>MedicationRequest.identifier</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -501,9 +538,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -519,22 +553,22 @@
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t>処方箋内部の剤グループとしてのRp番号</t>
-  </si>
-  <si>
-    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
-  </si>
-  <si>
-    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:rpNumber.id</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>処方箋に対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -556,26 +590,25 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.extension</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.use</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.use</t>
@@ -608,7 +641,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.type</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -645,16 +678,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.system</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)についてのsystem値</t>
-  </si>
-  <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -663,7 +696,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -675,19 +708,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.value</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>Rp番号(剤グループ番号)</t>
-  </si>
-  <si>
-    <t>Rp番号(剤グループ番号)。"1"など。</t>
-  </si>
-  <si>
-    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -699,7 +732,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.period</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -724,7 +757,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:rpNumber.assigner</t>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.assigner</t>
@@ -750,117 +783,6 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp</t>
-  </si>
-  <si>
-    <t>orderInRp</t>
-  </si>
-  <si>
-    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
-  </si>
-  <si>
-    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
-  </si>
-  <si>
-    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.system</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
-  </si>
-  <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.value</t>
-  </si>
-  <si>
-    <t>RP番号内（剤グループ内）の連番</t>
-  </si>
-  <si>
-    <t>剤グループ内連番。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:orderInRp.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.11</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
@@ -1554,12 +1476,6 @@
     <t>MedicationRequest.dispenseRequest.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.dispenseRequest.extension:instructionForDispense</t>
   </si>
   <si>
@@ -1574,10 +1490,6 @@
   </si>
   <si>
     <t>薬剤単位の調剤指示を格納する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:expectedRepeatCount</t>
@@ -2405,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3399,7 +3311,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3418,17 +3330,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3465,16 +3375,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3498,7 +3406,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -3512,43 +3420,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3596,7 +3502,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3605,7 +3511,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3617,7 +3523,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -3631,18 +3537,20 @@
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3662,9 +3570,7 @@
       <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3701,17 +3607,19 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3720,69 +3628,69 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3830,7 +3738,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3842,30 +3750,30 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3876,7 +3784,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3888,15 +3796,17 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3933,65 +3843,65 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -4003,16 +3913,16 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4050,19 +3960,19 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4074,30 +3984,30 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4114,26 +4024,22 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4157,13 +4063,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4181,7 +4087,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4193,7 +4099,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4202,32 +4108,32 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -4236,23 +4142,21 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -4276,43 +4180,43 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4321,21 +4225,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4343,7 +4247,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4352,32 +4256,32 @@
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4395,13 +4299,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4419,7 +4323,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4440,21 +4344,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4462,7 +4366,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4477,18 +4381,20 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4512,13 +4418,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -4536,7 +4442,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4557,21 +4463,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4579,7 +4485,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4594,22 +4500,26 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>82</v>
@@ -4651,7 +4561,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4672,21 +4582,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4694,7 +4604,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4709,16 +4619,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4768,7 +4678,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4789,31 +4699,29 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4825,20 +4733,18 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4887,13 +4793,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4902,27 +4808,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4942,18 +4848,20 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5002,7 +4910,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5014,7 +4922,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -5023,25 +4931,27 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5060,16 +4970,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>140</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5107,19 +5017,19 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5131,30 +5041,30 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5171,26 +5081,22 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5214,13 +5120,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5238,7 +5144,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5250,7 +5156,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5259,32 +5165,32 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5293,23 +5199,21 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5333,43 +5237,43 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5378,21 +5282,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5400,7 +5304,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -5409,32 +5313,32 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5452,13 +5356,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5476,7 +5380,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5497,21 +5401,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5519,7 +5423,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5534,18 +5438,20 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>203</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5569,13 +5475,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>209</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5593,7 +5499,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5614,21 +5520,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5636,7 +5542,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5651,22 +5557,26 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -5708,7 +5618,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5729,21 +5639,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5751,7 +5661,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5766,16 +5676,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5825,7 +5735,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5846,25 +5756,23 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5882,20 +5790,18 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5944,13 +5850,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5959,27 +5865,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>160</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5999,18 +5905,20 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6059,7 +5967,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6071,7 +5979,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6080,53 +5988,53 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>140</v>
+        <v>263</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6152,55 +6060,55 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>260</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>172</v>
+        <v>268</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6208,10 +6116,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6228,26 +6136,24 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6271,13 +6177,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>186</v>
+        <v>274</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>275</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6295,7 +6201,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6310,27 +6216,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6338,7 +6244,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6347,26 +6253,24 @@
         <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6390,13 +6294,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>198</v>
+        <v>282</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>199</v>
+        <v>283</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6414,10 +6318,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>278</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>91</v>
@@ -6429,27 +6333,27 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6457,10 +6361,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6469,29 +6373,27 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6509,13 +6411,11 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6533,13 +6433,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6551,24 +6451,24 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>293</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6576,7 +6476,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6591,16 +6491,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6626,13 +6526,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6650,7 +6550,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>294</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6665,27 +6565,27 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>218</v>
+        <v>301</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6702,21 +6602,23 @@
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>304</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6765,7 +6667,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6786,21 +6688,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6823,17 +6725,15 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>310</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>231</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6882,7 +6782,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6903,34 +6803,32 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6939,19 +6837,19 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6977,13 +6875,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7001,13 +6899,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>148</v>
+        <v>314</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -7016,27 +6914,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>159</v>
+        <v>323</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>160</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7044,7 +6942,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -7056,18 +6954,20 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>168</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>169</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7116,10 +7016,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -7128,41 +7028,41 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>172</v>
+        <v>332</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7174,16 +7074,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>336</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>337</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>338</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>140</v>
+        <v>339</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7221,54 +7121,54 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>341</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7279,32 +7179,30 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>111</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7328,13 +7226,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7352,13 +7250,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7367,27 +7265,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7395,7 +7293,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7410,20 +7308,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7447,13 +7341,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7471,7 +7365,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7486,27 +7380,27 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>357</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>201</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7514,7 +7408,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7529,26 +7423,24 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>105</v>
+        <v>361</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>362</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>363</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7590,7 +7482,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>360</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7605,27 +7497,27 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>210</v>
+        <v>332</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>366</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7633,7 +7525,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7645,19 +7537,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>367</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>270</v>
+        <v>369</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>271</v>
+        <v>348</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7707,7 +7599,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>366</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7722,27 +7614,27 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>218</v>
+        <v>371</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>373</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7765,15 +7657,17 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7798,13 +7692,11 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7822,7 +7714,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7837,27 +7729,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>226</v>
+        <v>379</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7877,19 +7769,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>231</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>232</v>
+        <v>383</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>233</v>
+        <v>348</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7939,7 +7831,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>234</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7960,21 +7852,21 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>235</v>
+        <v>384</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>236</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7982,31 +7874,31 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>111</v>
+        <v>202</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>388</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>290</v>
+        <v>389</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,13 +7924,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>273</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>291</v>
+        <v>390</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>292</v>
+        <v>391</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8056,13 +7948,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8071,27 +7963,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>294</v>
+        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>296</v>
+        <v>395</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>297</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8102,7 +7994,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8114,16 +8006,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>398</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>298</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
+        <v>400</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>299</v>
+        <v>401</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8149,13 +8041,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8173,13 +8065,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8188,16 +8080,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>403</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8097,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8216,31 +8108,31 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>308</v>
+        <v>408</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8266,13 +8158,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8290,13 +8182,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8305,16 +8197,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>311</v>
+        <v>409</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>312</v>
+        <v>410</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8214,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8345,19 +8237,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>407</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>317</v>
+        <v>413</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8383,11 +8275,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8405,7 +8299,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8423,13 +8317,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8437,10 +8331,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8451,7 +8345,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8463,16 +8357,16 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>111</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>416</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8498,13 +8392,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8522,13 +8416,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8537,16 +8431,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>418</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>419</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8554,10 +8448,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8574,24 +8468,24 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>331</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>421</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8639,7 +8533,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8654,13 +8548,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>425</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8565,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8694,18 +8588,20 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>337</v>
+        <v>202</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8730,13 +8626,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8754,7 +8650,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>426</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8775,7 +8671,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>432</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8786,10 +8682,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8797,10 +8693,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8809,19 +8705,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>434</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8847,13 +8743,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8871,13 +8767,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8886,27 +8782,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>347</v>
+        <v>437</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>349</v>
+        <v>438</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8914,10 +8810,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8926,19 +8822,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>440</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>356</v>
+        <v>443</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8988,13 +8884,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -9003,27 +8899,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>444</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>445</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>359</v>
+        <v>446</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9034,7 +8930,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9046,16 +8942,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>363</v>
+        <v>448</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>449</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>449</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>450</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9105,13 +9001,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9120,27 +9016,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>368</v>
+        <v>451</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9151,7 +9047,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9163,17 +9059,15 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>372</v>
+        <v>453</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>454</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9222,13 +9116,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>452</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9237,16 +9131,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>457</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9148,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9265,7 +9159,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>91</v>
@@ -9277,16 +9171,16 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>178</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>459</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>460</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9337,7 +9231,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>181</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9349,30 +9243,30 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>182</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9383,7 +9277,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9392,20 +9286,18 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>388</v>
+        <v>136</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>137</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9442,43 +9334,41 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>188</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9486,12 +9376,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9500,7 +9392,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9512,17 +9404,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>395</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9571,31 +9461,31 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>188</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9603,12 +9493,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>467</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9626,20 +9518,18 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>469</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9664,11 +9554,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9686,28 +9578,28 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>188</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9718,44 +9610,46 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>474</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
+        <v>475</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9803,19 +9697,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>476</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9824,10 +9718,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>134</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9835,10 +9729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9849,7 +9743,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9861,16 +9755,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>453</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>478</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>479</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>416</v>
+        <v>480</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9896,13 +9790,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9920,13 +9814,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9935,27 +9829,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9966,7 +9860,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9978,17 +9872,15 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>425</v>
+        <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>179</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10037,31 +9929,31 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>181</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>430</v>
+        <v>182</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10069,14 +9961,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>483</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10092,19 +9984,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>136</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>185</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>186</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>435</v>
+        <v>157</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10154,7 +10046,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>188</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10166,16 +10058,16 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>437</v>
+        <v>182</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10186,14 +10078,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10206,24 +10098,26 @@
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10271,7 +10165,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>476</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10283,7 +10177,7 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10292,7 +10186,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>134</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10197,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10317,7 +10211,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10326,19 +10220,19 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>487</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>444</v>
+        <v>488</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>489</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10388,42 +10282,42 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>103</v>
+        <v>490</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>446</v>
+        <v>491</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>493</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10443,21 +10337,21 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>494</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10505,7 +10399,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>493</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,13 +10414,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>452</v>
+        <v>497</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10537,10 +10431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,16 +10457,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>192</v>
+        <v>494</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10598,13 +10492,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10622,7 +10516,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10643,7 +10537,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>459</v>
+        <v>497</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10548,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10668,7 +10562,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10680,18 +10574,20 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>232</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>503</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10739,13 +10635,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10754,13 +10650,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10771,10 +10667,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10785,7 +10681,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10797,17 +10693,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>178</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>179</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10856,28 +10750,28 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>181</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>473</v>
+        <v>182</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10888,14 +10782,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>509</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10914,16 +10808,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>136</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>185</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>186</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>477</v>
+        <v>157</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10961,19 +10855,19 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>188</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10985,7 +10879,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10994,7 +10888,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>182</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11005,10 +10899,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>510</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11028,18 +10922,20 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>480</v>
+        <v>352</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>511</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11088,7 +10984,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>514</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11097,7 +10993,7 @@
         <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11106,24 +11002,24 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>82</v>
+        <v>517</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11143,23 +11039,27 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>352</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>519</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q75" s="2"/>
+      <c r="Q75" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="R75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11203,7 +11103,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>171</v>
+        <v>523</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11212,10 +11112,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11224,21 +11124,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>172</v>
+        <v>524</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>526</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11249,7 +11149,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11261,15 +11161,17 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>527</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>530</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11306,56 +11208,56 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>178</v>
+        <v>526</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>82</v>
+        <v>533</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>534</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11364,7 +11266,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11376,15 +11278,17 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11433,19 +11337,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>178</v>
+        <v>534</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>496</v>
+        <v>147</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>490</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11454,25 +11358,23 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11493,15 +11395,17 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11550,28 +11454,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>178</v>
+        <v>537</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11582,46 +11486,42 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>504</v>
+        <v>179</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11669,19 +11569,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>181</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11690,7 +11590,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11701,21 +11601,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11727,16 +11627,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>480</v>
+        <v>136</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>508</v>
+        <v>185</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>509</v>
+        <v>186</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>510</v>
+        <v>157</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11774,31 +11674,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>507</v>
+        <v>188</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11807,7 +11707,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>182</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11718,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11841,19 +11741,23 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>168</v>
+        <v>546</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>169</v>
+        <v>547</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>550</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11901,7 +11805,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>171</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11913,7 +11817,7 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11922,59 +11826,61 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>172</v>
+        <v>552</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>138</v>
+        <v>555</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11994,13 +11900,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12018,19 +11924,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>178</v>
+        <v>561</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12039,63 +11945,61 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>172</v>
+        <v>562</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>504</v>
+        <v>565</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>146</v>
+        <v>567</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>82</v>
@@ -12137,19 +12041,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>569</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12158,21 +12062,21 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>134</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>572</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12192,27 +12096,27 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>105</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>573</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -12254,7 +12158,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12263,10 +12167,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>496</v>
+        <v>578</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>520</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12275,21 +12179,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>522</v>
+        <v>571</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12309,27 +12213,29 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>524</v>
+        <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>525</v>
+        <v>581</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>526</v>
+        <v>582</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>82</v>
@@ -12371,7 +12277,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>586</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12392,21 +12298,21 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12429,16 +12335,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>589</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>590</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>530</v>
+        <v>591</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>519</v>
+        <v>348</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12488,7 +12394,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>588</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12509,10 +12415,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>527</v>
+        <v>592</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12520,10 +12426,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>593</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>593</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12546,20 +12452,16 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>222</v>
+        <v>453</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>532</v>
+        <v>594</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12607,7 +12509,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>593</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12625,10 +12527,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>536</v>
+        <v>596</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>537</v>
+        <v>597</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12639,10 +12541,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>598</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>598</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12665,13 +12567,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12722,7 +12624,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12743,7 +12645,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12754,14 +12656,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>599</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12780,16 +12682,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12827,19 +12729,19 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12860,7 +12762,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12871,44 +12773,46 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>136</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>542</v>
+        <v>475</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -12956,19 +12860,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>476</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12977,21 +12881,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>134</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>601</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>601</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12999,7 +12903,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>91</v>
@@ -13011,27 +12915,25 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>202</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>549</v>
+        <v>594</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>550</v>
+        <v>602</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>551</v>
+        <v>603</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>552</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13051,13 +12953,11 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>604</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13075,16 +12975,16 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>601</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13093,24 +12993,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>605</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>555</v>
+        <v>606</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13133,16 +13033,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>557</v>
+        <v>202</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>608</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>609</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>560</v>
+        <v>610</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13168,13 +13068,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>612</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13192,7 +13092,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13210,24 +13110,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>561</v>
+        <v>613</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>562</v>
+        <v>614</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>563</v>
+        <v>615</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>616</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>616</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,16 +13150,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>617</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>348</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13309,7 +13209,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13318,44 +13218,44 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>520</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>621</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>622</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>622</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13367,16 +13267,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>624</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>626</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>570</v>
+        <v>627</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,13 +13326,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>622</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13444,10 +13344,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13358,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13472,7 +13372,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13484,15 +13384,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>168</v>
+        <v>630</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>631</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13541,1907 +13443,33 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>171</v>
+        <v>629</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>82</v>
+        <v>634</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>172</v>
+        <v>635</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="R98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y107" s="2"/>
-      <c r="Z107" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3551" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -435,21 +435,21 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -459,44 +459,7 @@
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>MedicationRequest.extension:rpNumber</t>
-  </si>
-  <si>
-    <t>rpNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_RpNumber}
-</t>
-  </si>
-  <si>
-    <t>Rp番号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:drugNumber</t>
-  </si>
-  <si>
-    <t>drugNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationRequest_DrugNumber}
-</t>
-  </si>
-  <si>
-    <t>薬剤番号</t>
-  </si>
-  <si>
-    <t>薬剤番号を表現する拡張</t>
-  </si>
-  <si>
     <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
@@ -507,9 +470,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -517,6 +477,9 @@
   </si>
   <si>
     <t>MedicationRequest.identifier</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -538,6 +501,9 @@
 </t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -553,22 +519,22 @@
     <t>ORC-2-Placer Order Number / ORC-3-Filler Order Number</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
+    <t>MedicationRequest.identifier:rpNumber</t>
+  </si>
+  <si>
+    <t>rpNumber</t>
+  </si>
+  <si>
+    <t>処方箋内部の剤グループとしてのRp番号</t>
+  </si>
+  <si>
+    <t>処方箋内で同一用法の薬剤を慣用的にまとめて、Rpに番号をつけて剤グループとして一括指定されることがある。このスライスでは剤グループに対して割り振られたRp番号を記録する。</t>
+  </si>
+  <si>
+    <t>剤グループに複数の薬剤が含まれる場合、このグループ内の薬剤には同じRp番号が割り振られる。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:rpNumber.id</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.id</t>
@@ -590,25 +556,26 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
+    <t>MedicationRequest.identifier:rpNumber.extension</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.extension</t>
   </si>
   <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
+    <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.use</t>
@@ -641,7 +608,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
+    <t>MedicationRequest.identifier:rpNumber.type</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.type</t>
@@ -678,16 +645,16 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+    <t>MedicationRequest.identifier:rpNumber.system</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Rp番号(剤グループ番号)についてのsystem値</t>
+  </si>
+  <si>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -696,7 +663,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.11</t>
+    <t>urn:oid:1.2.392.100495.20.3.81</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -708,19 +675,19 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
+    <t>MedicationRequest.identifier:rpNumber.value</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.value</t>
   </si>
   <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>Rp番号(剤グループ番号)</t>
+  </si>
+  <si>
+    <t>Rp番号(剤グループ番号)。"1"など。</t>
+  </si>
+  <si>
+    <t>value は string型であり、数値はゼロサプレス、つまり、'01'でなく'1'と指定すること。</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -732,7 +699,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
+    <t>MedicationRequest.identifier:rpNumber.period</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.period</t>
@@ -757,7 +724,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
+    <t>MedicationRequest.identifier:rpNumber.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier.assigner</t>
@@ -783,6 +750,117 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp</t>
+  </si>
+  <si>
+    <t>orderInRp</t>
+  </si>
+  <si>
+    <t>同一RP番号（剤グループ）での薬剤の表記順</t>
+  </si>
+  <si>
+    <t>同一剤グループでの薬剤を表記する際の順番。XML形式と異なりJSON形式の場合、表記順は項目の順序を意味しない。したがって、薬剤の記載順を別に規定する必要があるためIDを用いて表現する。</t>
+  </si>
+  <si>
+    <t>同一剤グループ内での薬剤の順番を1から順の番号で示す。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.system</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
+  </si>
+  <si>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.82</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.value</t>
+  </si>
+  <si>
+    <t>RP番号内（剤グループ内）の連番</t>
+  </si>
+  <si>
+    <t>剤グループ内連番。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:orderInRp.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>requestIdentifierCommon</t>
+  </si>
+  <si>
+    <t>処方箋に対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+  </si>
+  <si>
+    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier</t>
@@ -1476,6 +1554,12 @@
     <t>MedicationRequest.dispenseRequest.extension</t>
   </si>
   <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.extension:instructionForDispense</t>
   </si>
   <si>
@@ -1490,6 +1574,10 @@
   </si>
   <si>
     <t>薬剤単位の調剤指示を格納する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.extension:expectedRepeatCount</t>
@@ -2317,7 +2405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
@@ -3311,7 +3399,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3330,15 +3418,17 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3375,14 +3465,16 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -3406,7 +3498,7 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>82</v>
@@ -3420,41 +3512,43 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3502,7 +3596,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3511,7 +3605,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3523,7 +3617,7 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>82</v>
@@ -3537,20 +3631,18 @@
         <v>148</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>82</v>
@@ -3570,7 +3662,9 @@
       <c r="M11" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3607,19 +3701,17 @@
         <v>82</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3628,69 +3720,69 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3738,7 +3830,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3750,30 +3842,30 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3784,7 +3876,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3796,17 +3888,15 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3843,65 +3933,65 @@
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>82</v>
@@ -3913,16 +4003,16 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3960,19 +4050,19 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3984,30 +4074,30 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4024,22 +4114,26 @@
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4063,13 +4157,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4087,7 +4181,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4099,7 +4193,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4108,32 +4202,32 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>82</v>
@@ -4142,21 +4236,23 @@
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -4180,43 +4276,43 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4225,21 +4321,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4247,7 +4343,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -4256,32 +4352,32 @@
         <v>82</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>82</v>
+        <v>208</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4299,13 +4395,13 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4323,7 +4419,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4344,21 +4440,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4366,7 +4462,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>91</v>
@@ -4381,20 +4477,18 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -4418,13 +4512,13 @@
         <v>82</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>82</v>
@@ -4442,7 +4536,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4463,21 +4557,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4485,7 +4579,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4500,26 +4594,22 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>82</v>
@@ -4561,7 +4651,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4582,21 +4672,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4604,7 +4694,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>91</v>
@@ -4619,16 +4709,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4678,7 +4768,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4699,29 +4789,31 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4733,18 +4825,20 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4793,13 +4887,13 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
@@ -4808,27 +4902,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4848,20 +4942,18 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4910,7 +5002,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4922,7 +5014,7 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -4931,27 +5023,25 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4970,16 +5060,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5017,19 +5107,19 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5041,30 +5131,30 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5081,22 +5171,26 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>178</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5120,13 +5214,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5144,7 +5238,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5156,7 +5250,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5165,32 +5259,32 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5199,21 +5293,23 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5237,43 +5333,43 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5282,21 +5378,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5304,7 +5400,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>91</v>
@@ -5313,32 +5409,32 @@
         <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>191</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>192</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5356,13 +5452,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5380,7 +5476,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5401,21 +5497,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>134</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5423,7 +5519,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
@@ -5438,20 +5534,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>203</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5475,13 +5569,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5499,7 +5593,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5520,21 +5614,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5542,7 +5636,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>91</v>
@@ -5557,26 +5651,22 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -5618,7 +5708,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5639,21 +5729,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5661,7 +5751,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
@@ -5676,16 +5766,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>178</v>
+        <v>230</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5735,7 +5825,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5756,23 +5846,25 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5790,18 +5882,20 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5850,13 +5944,13 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>148</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
@@ -5865,27 +5959,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>236</v>
+        <v>158</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>159</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>237</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5905,20 +5999,18 @@
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>241</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5967,7 +6059,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5979,7 +6071,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5988,53 +6080,53 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>245</v>
+        <v>172</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>261</v>
+        <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>262</v>
+        <v>175</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>263</v>
+        <v>140</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6060,55 +6152,55 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>268</v>
+        <v>172</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6116,10 +6208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6136,24 +6228,26 @@
         <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>271</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6177,13 +6271,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>273</v>
+        <v>185</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6201,7 +6295,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6216,27 +6310,27 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6244,7 +6338,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
@@ -6253,24 +6347,26 @@
         <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>193</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>194</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6294,13 +6390,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>282</v>
+        <v>198</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>283</v>
+        <v>199</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6318,10 +6414,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>91</v>
@@ -6333,27 +6429,27 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6361,10 +6457,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -6373,27 +6469,29 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>288</v>
+        <v>265</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6411,11 +6509,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6433,13 +6533,13 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>287</v>
+        <v>209</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6451,24 +6551,24 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>293</v>
+        <v>210</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>294</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6476,7 +6576,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
@@ -6491,16 +6591,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6526,13 +6626,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6550,7 +6650,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6565,27 +6665,27 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>301</v>
+        <v>218</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6602,23 +6702,21 @@
         <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>305</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6667,7 +6765,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6688,21 +6786,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>308</v>
+        <v>226</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6725,15 +6823,17 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6782,7 +6882,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6803,32 +6903,34 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>313</v>
+        <v>235</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6837,19 +6939,19 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>315</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6875,13 +6977,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6899,13 +7001,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>148</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6914,27 +7016,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>320</v>
+        <v>156</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>321</v>
+        <v>157</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>322</v>
+        <v>158</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>323</v>
+        <v>159</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>324</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>167</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6942,7 +7044,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>91</v>
@@ -6954,20 +7056,18 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>169</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7016,10 +7116,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>171</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>91</v>
@@ -7028,41 +7128,41 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>332</v>
+        <v>172</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>174</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7074,16 +7174,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>336</v>
+        <v>137</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>337</v>
+        <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>338</v>
+        <v>175</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>339</v>
+        <v>140</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7121,54 +7221,54 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>341</v>
+        <v>172</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>180</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7179,30 +7279,32 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>181</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7226,13 +7328,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7250,13 +7352,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>188</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7265,27 +7367,27 @@
         <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>350</v>
+        <v>189</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>191</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7293,7 +7395,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7308,16 +7410,20 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>193</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7341,13 +7447,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7365,7 +7471,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7380,27 +7486,27 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>357</v>
+        <v>189</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>359</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>360</v>
+        <v>282</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>360</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7408,7 +7514,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7423,24 +7529,26 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>265</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
+        <v>266</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>82</v>
+        <v>283</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7482,7 +7590,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>360</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7497,27 +7605,27 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>210</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7525,7 +7633,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7537,19 +7645,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>269</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
+        <v>270</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7599,7 +7707,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7614,27 +7722,27 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>371</v>
+        <v>218</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>221</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7657,17 +7765,15 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>374</v>
+        <v>223</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7692,11 +7798,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7714,7 +7822,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7729,27 +7837,27 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>379</v>
+        <v>226</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>380</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>380</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7769,19 +7877,19 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>231</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>232</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>348</v>
+        <v>233</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7831,7 +7939,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>380</v>
+        <v>234</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7852,21 +7960,21 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>384</v>
+        <v>235</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>287</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7874,31 +7982,31 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>288</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>289</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>389</v>
+        <v>290</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7924,13 +8032,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>273</v>
+        <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>390</v>
+        <v>291</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>391</v>
+        <v>292</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7948,13 +8056,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>287</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7963,27 +8071,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>392</v>
+        <v>293</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>294</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>295</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>395</v>
+        <v>296</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>297</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7994,7 +8102,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8006,16 +8114,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>398</v>
+        <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>399</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>400</v>
+        <v>298</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>401</v>
+        <v>299</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8041,13 +8149,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8065,13 +8173,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>297</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -8080,16 +8188,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>402</v>
+        <v>303</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>403</v>
+        <v>304</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8097,10 +8205,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8108,31 +8216,31 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>306</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>307</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>408</v>
+        <v>308</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8158,13 +8266,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8182,13 +8290,13 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
@@ -8197,16 +8305,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>311</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>410</v>
+        <v>312</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8214,10 +8322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8237,19 +8345,19 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>407</v>
+        <v>316</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>413</v>
+        <v>317</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8275,13 +8383,11 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8299,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8317,13 +8423,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8331,10 +8437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8345,7 +8451,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8357,16 +8463,16 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8392,13 +8498,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8416,13 +8522,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8431,16 +8537,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>418</v>
+        <v>327</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>419</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8448,10 +8554,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8468,24 +8574,24 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>421</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8533,7 +8639,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8548,13 +8654,13 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>425</v>
+        <v>335</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8565,10 +8671,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>426</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>426</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8588,20 +8694,18 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>202</v>
+        <v>337</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8626,13 +8730,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8650,7 +8754,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>426</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8671,7 +8775,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8682,10 +8786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8693,10 +8797,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8705,19 +8809,19 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>434</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>342</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>343</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8743,13 +8847,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8767,13 +8871,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8782,27 +8886,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>437</v>
+        <v>347</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>438</v>
+        <v>349</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8810,10 +8914,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>82</v>
@@ -8822,19 +8926,19 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>440</v>
+        <v>353</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>441</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>442</v>
+        <v>355</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>443</v>
+        <v>356</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8884,13 +8988,13 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>439</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>82</v>
@@ -8899,27 +9003,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>444</v>
+        <v>357</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>445</v>
+        <v>358</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>446</v>
+        <v>359</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8930,7 +9034,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -8942,16 +9046,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>448</v>
+        <v>363</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>449</v>
+        <v>365</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>450</v>
+        <v>366</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9001,13 +9105,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9016,27 +9120,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>451</v>
+        <v>368</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9047,7 +9151,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9059,15 +9163,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>453</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9116,13 +9222,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9131,16 +9237,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>457</v>
+        <v>377</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9148,10 +9254,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9159,7 +9265,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>91</v>
@@ -9171,16 +9277,16 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>178</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9231,7 +9337,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>181</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9243,30 +9349,30 @@
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>182</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9277,7 +9383,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9286,18 +9392,20 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>388</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>137</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9334,41 +9442,43 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>188</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9376,14 +9486,12 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9392,7 +9500,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9404,15 +9512,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>464</v>
+        <v>394</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>395</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9461,31 +9571,31 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>188</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9493,14 +9603,12 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9518,18 +9626,20 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>469</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>401</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9554,13 +9664,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9578,28 +9686,28 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9610,46 +9718,44 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>136</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>474</v>
+        <v>409</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>475</v>
+        <v>410</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9697,19 +9803,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>476</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9824,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>134</v>
+        <v>411</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9729,10 +9835,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>477</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9743,7 +9849,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9755,16 +9861,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>453</v>
+        <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>478</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>479</v>
+        <v>415</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>480</v>
+        <v>416</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9790,13 +9896,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9814,13 +9920,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>477</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9829,27 +9935,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>481</v>
+        <v>421</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>482</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9860,7 +9966,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9872,15 +9978,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>178</v>
+        <v>425</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>179</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9929,31 +10037,31 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>294</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>182</v>
+        <v>430</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -9961,14 +10069,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>483</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9984,19 +10092,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>432</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>185</v>
+        <v>433</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>186</v>
+        <v>434</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>157</v>
+        <v>435</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10046,7 +10154,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>188</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10058,16 +10166,16 @@
         <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>182</v>
+        <v>437</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10078,14 +10186,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10098,26 +10206,24 @@
         <v>82</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10165,7 +10271,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>476</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10177,7 +10283,7 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
@@ -10186,7 +10292,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>134</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10197,10 +10303,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10211,7 +10317,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10220,19 +10326,19 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>487</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>488</v>
+        <v>444</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>489</v>
+        <v>375</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10282,42 +10388,42 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>485</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>490</v>
+        <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10337,21 +10443,21 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>494</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10399,7 +10505,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>493</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10414,13 +10520,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>497</v>
+        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10431,10 +10537,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10457,16 +10563,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>494</v>
+        <v>192</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>499</v>
+        <v>454</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10492,13 +10598,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10516,7 +10622,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10537,7 +10643,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10548,10 +10654,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10562,7 +10668,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10574,20 +10680,18 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>232</v>
+        <v>461</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>463</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10635,13 +10739,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10650,13 +10754,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>507</v>
+        <v>465</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10667,10 +10771,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10681,7 +10785,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10693,15 +10797,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>178</v>
+        <v>467</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>179</v>
+        <v>468</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10750,28 +10856,28 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>181</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>182</v>
+        <v>473</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10782,14 +10888,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>509</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10808,16 +10914,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>136</v>
+        <v>475</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>185</v>
+        <v>476</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>186</v>
+        <v>476</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>157</v>
+        <v>477</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10855,19 +10961,19 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>188</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10879,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10888,7 +10994,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>182</v>
+        <v>478</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -10899,10 +11005,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10922,20 +11028,18 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>352</v>
+        <v>480</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -10984,7 +11088,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10993,7 +11097,7 @@
         <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11002,24 +11106,24 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>516</v>
+        <v>484</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>518</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11039,27 +11143,23 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>352</v>
+        <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>519</v>
+        <v>486</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q75" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11103,7 +11203,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>523</v>
+        <v>171</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11112,10 +11212,10 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
@@ -11124,21 +11224,21 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>524</v>
+        <v>172</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11149,7 +11249,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11161,17 +11261,15 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>527</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11208,56 +11306,56 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>526</v>
+        <v>178</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>533</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>534</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11266,7 +11364,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11278,17 +11376,15 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>535</v>
+        <v>494</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11337,19 +11433,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>534</v>
+        <v>178</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>147</v>
+        <v>496</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>490</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11358,23 +11454,25 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>537</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11395,17 +11493,15 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11454,28 +11550,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>537</v>
+        <v>178</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11486,42 +11582,46 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>179</v>
+        <v>504</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11569,19 +11669,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>181</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11590,7 +11690,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11601,21 +11701,21 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>544</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11627,16 +11727,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>136</v>
+        <v>480</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>185</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>186</v>
+        <v>509</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>157</v>
+        <v>510</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11674,31 +11774,31 @@
         <v>82</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>188</v>
+        <v>507</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11707,7 +11807,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>182</v>
+        <v>511</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11718,10 +11818,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11741,23 +11841,19 @@
         <v>82</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>546</v>
+        <v>168</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>547</v>
+        <v>169</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11805,7 +11901,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>551</v>
+        <v>171</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11817,7 +11913,7 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11826,61 +11922,59 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>552</v>
+        <v>172</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>555</v>
+        <v>138</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q82" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
         <v>82</v>
       </c>
@@ -11900,13 +11994,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -11924,19 +12018,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>561</v>
+        <v>178</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -11945,61 +12039,63 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>562</v>
+        <v>172</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>564</v>
+        <v>514</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>565</v>
+        <v>504</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O83" t="s" s="2">
-        <v>567</v>
+        <v>146</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>82</v>
@@ -12041,19 +12137,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>569</v>
+        <v>506</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12062,21 +12158,21 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>570</v>
+        <v>134</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>572</v>
+        <v>515</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>572</v>
+        <v>515</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12096,27 +12192,27 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>105</v>
+        <v>516</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>573</v>
+        <v>517</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>82</v>
@@ -12158,7 +12254,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12167,10 +12263,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>578</v>
+        <v>496</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12179,21 +12275,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>579</v>
+        <v>521</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>571</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12213,29 +12309,27 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>111</v>
+        <v>524</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>581</v>
+        <v>525</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>582</v>
+        <v>526</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>519</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>82</v>
@@ -12277,7 +12371,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>586</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12298,21 +12392,21 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>587</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12335,16 +12429,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>589</v>
+        <v>524</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>591</v>
+        <v>530</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>348</v>
+        <v>519</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12394,7 +12488,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12415,10 +12509,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>592</v>
+        <v>527</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12426,10 +12520,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12452,16 +12546,20 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>453</v>
+        <v>222</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12509,7 +12607,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12527,10 +12625,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>596</v>
+        <v>536</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>597</v>
+        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12541,10 +12639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>598</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>598</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12567,13 +12665,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12624,7 +12722,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12645,7 +12743,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12656,14 +12754,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>599</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>599</v>
+        <v>539</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12682,16 +12780,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12729,19 +12827,19 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12762,7 +12860,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12773,46 +12871,44 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>136</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>474</v>
+        <v>541</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>475</v>
+        <v>542</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -12860,19 +12956,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>476</v>
+        <v>544</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12881,21 +12977,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>134</v>
+        <v>546</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12903,7 +12999,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>91</v>
@@ -12915,25 +13011,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>202</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>594</v>
+        <v>549</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>602</v>
+        <v>550</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>603</v>
+        <v>551</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -12953,11 +13051,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -12975,16 +13075,16 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>553</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>545</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -12993,24 +13093,24 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>605</v>
+        <v>554</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>606</v>
+        <v>555</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13033,16 +13133,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>202</v>
+        <v>557</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>608</v>
+        <v>558</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>609</v>
+        <v>559</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>610</v>
+        <v>560</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13068,13 +13168,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>612</v>
+        <v>82</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13092,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>607</v>
+        <v>556</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13110,24 +13210,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>613</v>
+        <v>561</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>614</v>
+        <v>562</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>615</v>
+        <v>563</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>616</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13150,16 +13250,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>617</v>
+        <v>516</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>618</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>619</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>348</v>
+        <v>519</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13209,7 +13309,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>616</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13218,44 +13318,44 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>621</v>
+        <v>521</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13267,16 +13367,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>624</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>625</v>
+        <v>568</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>626</v>
+        <v>569</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>627</v>
+        <v>570</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13326,13 +13426,13 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
@@ -13344,10 +13444,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>628</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13358,10 +13458,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>629</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13372,7 +13472,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13384,17 +13484,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>630</v>
+        <v>168</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>631</v>
+        <v>169</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13443,33 +13541,1907 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
+      <c r="B105" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
+      <c r="H105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK95" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AK107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AM107" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AN95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO95" t="s" s="2">
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="O109" s="2"/>
+      <c r="P109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -654,7 +654,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
@@ -663,7 +663,7 @@
     <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -785,10 +785,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:orderInRp.value</t>
@@ -888,9 +888,6 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
@@ -7548,7 +7545,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7622,7 +7619,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>213</v>
@@ -7739,7 +7736,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>221</v>
@@ -7854,7 +7851,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>229</v>
@@ -7971,10 +7968,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8000,13 +7997,13 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8035,11 +8032,11 @@
         <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>292</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8056,7 +8053,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8071,16 +8068,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AM48" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8088,10 +8085,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8117,13 +8114,13 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8149,14 +8146,14 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="Y49" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="Y49" t="s" s="2">
+      <c r="Z49" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8173,7 +8170,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8188,13 +8185,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8202,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8234,13 +8231,13 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8269,11 +8266,11 @@
         <v>185</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8290,7 +8287,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8305,16 +8302,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8319,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8351,13 +8348,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8387,7 +8384,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8405,7 +8402,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8423,13 +8420,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8437,10 +8434,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8466,13 +8463,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8501,11 +8498,11 @@
         <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8522,7 +8519,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8537,16 +8534,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8554,10 +8551,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8580,16 +8577,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8639,7 +8636,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8660,7 +8657,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8668,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8697,13 +8694,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8754,7 +8751,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8775,7 +8772,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8786,10 +8783,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8815,13 +8812,13 @@
         <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8850,11 +8847,11 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8871,7 +8868,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8886,27 +8883,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>351</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8929,16 +8926,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8988,7 +8985,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9003,27 +9000,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9046,16 +9043,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9105,7 +9102,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9120,27 +9117,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9163,16 +9160,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9222,7 +9219,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9237,16 +9234,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AN58" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9251,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9280,13 +9277,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9337,7 +9334,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9352,27 +9349,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9395,16 +9392,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9454,7 +9451,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9469,16 +9466,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9486,10 +9483,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9512,16 +9509,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9571,7 +9568,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9586,16 +9583,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9600,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9632,13 +9629,13 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9664,11 +9661,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9686,7 +9683,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9701,13 +9698,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9715,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9744,16 +9741,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9803,7 +9800,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9824,10 +9821,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9835,10 +9832,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9864,13 +9861,13 @@
         <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9896,14 +9893,14 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9920,7 +9917,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9935,27 +9932,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,16 +9975,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10037,7 +10034,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10052,16 +10049,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AN65" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10069,10 +10066,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10095,16 +10092,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10154,7 +10151,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10169,13 +10166,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10186,10 +10183,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10215,13 +10212,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10271,7 +10268,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10292,7 +10289,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10300,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10329,16 +10326,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10388,7 +10385,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10403,13 +10400,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10420,10 +10417,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10449,14 +10446,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10505,7 +10502,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,13 +10517,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10537,10 +10534,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10566,13 +10563,13 @@
         <v>192</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10598,14 +10595,14 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10622,7 +10619,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10643,7 +10640,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10651,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10680,16 +10677,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10739,7 +10736,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10751,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10771,10 +10768,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10797,16 +10794,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10856,7 +10853,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10871,13 +10868,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10885,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10914,16 +10911,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10973,7 +10970,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10994,7 +10991,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11005,10 +11002,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11031,13 +11028,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11088,7 +11085,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11106,10 +11103,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11120,10 +11117,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11149,10 +11146,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11235,10 +11232,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11264,10 +11261,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11348,13 +11345,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11376,13 +11373,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11442,7 +11439,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11465,13 +11462,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11493,13 +11490,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11559,7 +11556,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11582,14 +11579,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11611,10 +11608,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11669,7 +11666,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11701,10 +11698,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11727,16 +11724,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11786,7 +11783,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11807,7 +11804,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11815,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11933,10 +11930,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12050,14 +12047,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12079,10 +12076,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12137,7 +12134,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12166,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,16 +12192,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12254,7 +12251,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12263,33 +12260,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12312,16 +12309,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>526</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12371,7 +12368,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12392,7 +12389,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12403,10 +12400,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12429,16 +12426,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="N86" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12488,7 +12485,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12509,7 +12506,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12520,10 +12517,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12549,16 +12546,16 @@
         <v>222</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12607,7 +12604,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12625,10 +12622,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12639,10 +12636,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12754,10 +12751,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12871,10 +12868,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12897,16 +12894,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12956,16 +12953,16 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12977,21 +12974,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>547</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13014,69 +13011,69 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13084,7 +13081,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13096,21 +13093,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13133,16 +13130,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13192,7 +13189,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13210,24 +13207,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>563</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,16 +13247,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13309,7 +13306,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13318,33 +13315,33 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AJ93" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="AK93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>522</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13367,16 +13364,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,7 +13423,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13444,10 +13441,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13455,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13573,10 +13570,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13690,10 +13687,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13716,19 +13713,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13777,7 +13774,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13798,21 +13795,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>583</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13838,20 +13835,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13875,28 +13872,28 @@
         <v>185</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13917,21 +13914,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>593</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13957,63 +13954,63 @@
         <v>168</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14034,21 +14031,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>601</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14074,72 +14071,72 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14151,21 +14148,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14191,65 +14188,65 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14270,21 +14267,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14307,16 +14304,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M102" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="N102" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14366,7 +14363,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14387,10 +14384,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14398,10 +14395,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14424,13 +14421,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14481,7 +14478,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14499,10 +14496,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>627</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14513,10 +14510,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14628,10 +14625,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14745,14 +14742,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14774,10 +14771,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14832,7 +14829,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14864,10 +14861,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14893,13 +14890,13 @@
         <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14929,7 +14926,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14947,7 +14944,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14965,24 +14962,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>636</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15008,13 +15005,13 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15040,14 +15037,14 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="Z108" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="Z108" t="s" s="2">
-        <v>642</v>
-      </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15064,7 +15061,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15082,24 +15079,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>645</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15122,16 +15119,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>649</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15181,7 +15178,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15196,13 +15193,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15213,14 +15210,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15239,16 +15236,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>656</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15298,7 +15295,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15319,7 +15316,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15330,10 +15327,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,16 +15353,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15415,7 +15412,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15430,13 +15427,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -888,6 +888,9 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifier.value</t>
@@ -7545,7 +7548,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7619,7 +7622,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>213</v>
@@ -7736,7 +7739,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>221</v>
@@ -7851,7 +7854,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>229</v>
@@ -7968,10 +7971,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7997,13 +8000,13 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,10 +8035,10 @@
         <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8053,7 +8056,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8068,16 +8071,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8085,10 +8088,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8114,13 +8117,13 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8146,13 +8149,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8170,7 +8173,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8185,13 +8188,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8202,10 +8205,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8231,13 +8234,13 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8266,10 +8269,10 @@
         <v>185</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8287,7 +8290,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8302,16 +8305,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8319,10 +8322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8348,13 +8351,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8384,7 +8387,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8402,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8420,13 +8423,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8434,10 +8437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8463,13 +8466,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8498,10 +8501,10 @@
         <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8519,7 +8522,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8534,16 +8537,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8551,10 +8554,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8577,16 +8580,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8636,7 +8639,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8657,7 +8660,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8668,10 +8671,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8694,13 +8697,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8751,7 +8754,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8772,7 +8775,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8783,10 +8786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8812,13 +8815,13 @@
         <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8847,10 +8850,10 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8868,7 +8871,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8883,27 +8886,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8926,16 +8929,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8985,7 +8988,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9000,27 +9003,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9043,16 +9046,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9102,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9117,27 +9120,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9160,16 +9163,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9219,7 +9222,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9234,16 +9237,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9251,10 +9254,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9277,13 +9280,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9334,7 +9337,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9349,27 +9352,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9392,16 +9395,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9451,7 +9454,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9466,16 +9469,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9483,10 +9486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9509,16 +9512,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9568,7 +9571,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9583,16 +9586,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9600,10 +9603,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9629,13 +9632,13 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9661,11 +9664,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9683,7 +9686,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9698,13 +9701,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9715,10 +9718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9741,16 +9744,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9800,7 +9803,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9821,10 +9824,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9832,10 +9835,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9861,13 +9864,13 @@
         <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9893,13 +9896,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9917,7 +9920,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9932,27 +9935,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9975,16 +9978,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10034,7 +10037,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10049,16 +10052,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10066,10 +10069,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10092,16 +10095,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10151,7 +10154,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10166,13 +10169,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10183,10 +10186,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10212,13 +10215,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10268,7 +10271,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10289,7 +10292,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10300,10 +10303,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10326,16 +10329,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10385,7 +10388,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10400,13 +10403,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10417,10 +10420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10446,14 +10449,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10502,7 +10505,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10517,13 +10520,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10534,10 +10537,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,13 +10566,13 @@
         <v>192</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10595,13 +10598,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10619,7 +10622,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10640,7 +10643,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10651,10 +10654,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10677,16 +10680,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10736,7 +10739,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10751,13 +10754,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10768,10 +10771,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10794,16 +10797,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10853,7 +10856,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10868,13 +10871,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10885,10 +10888,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10911,16 +10914,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10970,7 +10973,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10991,7 +10994,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11002,10 +11005,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11028,13 +11031,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11085,7 +11088,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11103,10 +11106,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11117,10 +11120,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11146,10 +11149,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11232,10 +11235,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11261,10 +11264,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11345,13 +11348,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11373,13 +11376,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11439,7 +11442,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11462,13 +11465,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11490,13 +11493,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11556,7 +11559,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11579,14 +11582,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11608,10 +11611,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11666,7 +11669,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11698,10 +11701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11724,16 +11727,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11783,7 +11786,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11804,7 +11807,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11815,10 +11818,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11930,10 +11933,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12047,14 +12050,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12076,10 +12079,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12134,7 +12137,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12166,10 +12169,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12192,16 +12195,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12251,7 +12254,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12260,10 +12263,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12272,21 +12275,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12309,16 +12312,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12368,7 +12371,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12389,7 +12392,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12400,10 +12403,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12426,16 +12429,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12485,7 +12488,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12506,7 +12509,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12517,10 +12520,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12546,16 +12549,16 @@
         <v>222</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12604,7 +12607,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12622,10 +12625,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12636,10 +12639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12751,10 +12754,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12868,10 +12871,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12894,16 +12897,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12953,7 +12956,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12962,7 +12965,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12974,21 +12977,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13011,23 +13014,23 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
@@ -13072,7 +13075,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13081,7 +13084,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13093,21 +13096,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13130,16 +13133,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13189,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13207,24 +13210,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13247,16 +13250,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13306,7 +13309,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13315,10 +13318,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13327,21 +13330,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13364,16 +13367,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13423,7 +13426,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13441,10 +13444,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13455,10 +13458,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13570,10 +13573,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13687,10 +13690,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13713,19 +13716,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13774,7 +13777,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13795,21 +13798,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13835,20 +13838,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13872,10 +13875,10 @@
         <v>185</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13893,7 +13896,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13914,21 +13917,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13954,21 +13957,21 @@
         <v>168</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14010,7 +14013,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14031,21 +14034,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14071,21 +14074,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14127,7 +14130,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14136,7 +14139,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14148,21 +14151,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14188,23 +14191,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14246,7 +14249,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14267,21 +14270,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14304,16 +14307,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14363,7 +14366,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14384,10 +14387,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14395,10 +14398,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14421,13 +14424,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14478,7 +14481,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14496,10 +14499,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14510,10 +14513,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14625,10 +14628,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14742,14 +14745,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14771,10 +14774,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14829,7 +14832,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14861,10 +14864,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14890,13 +14893,13 @@
         <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14926,7 +14929,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14944,7 +14947,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14962,24 +14965,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15005,13 +15008,13 @@
         <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15037,13 +15040,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15061,7 +15064,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15079,24 +15082,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15119,16 +15122,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15178,7 +15181,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15193,13 +15196,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15210,14 +15213,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15236,16 +15239,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15295,7 +15298,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15316,7 +15319,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15327,10 +15330,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15353,16 +15356,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15412,7 +15415,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15427,13 +15430,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -581,22 +581,22 @@
     <t>MedicationRequest.identifier.use</t>
   </si>
   <si>
-    <t>通常|公式|温度|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -618,22 +618,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -657,10 +657,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -712,7 +712,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -737,10 +737,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -818,7 +818,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -836,7 +836,7 @@
     <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -851,10 +851,10 @@
     <t>一意の値 / The value that is unique</t>
   </si>
   <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
@@ -1654,7 +1654,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -1939,7 +1939,7 @@
     <t>一部のユニット表現システムのユニットのコンピューター処理可能な形式。 / A computer processable form of the unit in some unit representation system.</t>
   </si>
   <si>
-    <t>優先システムはUCUMですが、スノムCTは（慣習ユニットに）または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+    <t>優先システムはUCUMですが、独自の単位にはSNOMED-CT、または通貨にISO 4217を使用することもできます。使用のコンテキストには、特定のシステムからのコードがさらに必要になる場合があります。 / The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
   </si>
   <si>
     <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するメタデータ / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -575,6 +575,10 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
@@ -603,6 +607,10 @@
   </si>
   <si>
     <t>Identifier.use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -818,7 +826,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -4074,7 +4082,7 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4094,10 +4102,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4123,16 +4131,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4157,13 +4165,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4181,7 +4189,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4193,7 +4201,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4202,7 +4210,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4213,10 +4221,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4239,19 +4247,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4276,13 +4284,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4300,7 +4308,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4312,7 +4320,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4321,21 +4329,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4361,23 +4369,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4419,7 +4427,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4431,7 +4439,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4440,21 +4448,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4480,13 +4488,13 @@
         <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4536,7 +4544,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4548,7 +4556,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -4557,21 +4565,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4594,13 +4602,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4651,7 +4659,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4663,7 +4671,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4672,21 +4680,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4709,16 +4717,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4768,7 +4776,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4780,7 +4788,7 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4789,24 +4797,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4831,13 +4839,13 @@
         <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4919,7 +4927,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>167</v>
@@ -5034,7 +5042,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>174</v>
@@ -5131,7 +5139,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5151,10 +5159,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5180,16 +5188,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5214,13 +5222,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5238,7 +5246,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5250,7 +5258,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5259,7 +5267,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5270,10 +5278,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5296,19 +5304,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5333,13 +5341,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5357,7 +5365,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5369,7 +5377,7 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5378,21 +5386,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5418,23 +5426,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5476,7 +5484,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5488,7 +5496,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5497,21 +5505,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5537,13 +5545,13 @@
         <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5593,7 +5601,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5605,7 +5613,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5614,21 +5622,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5651,13 +5659,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5708,7 +5716,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5720,7 +5728,7 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5729,21 +5737,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5766,16 +5774,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5825,7 +5833,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5837,7 +5845,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5846,24 +5854,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5888,13 +5896,13 @@
         <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5976,7 +5984,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>167</v>
@@ -6091,7 +6099,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>174</v>
@@ -6188,7 +6196,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6208,10 +6216,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6237,16 +6245,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6271,13 +6279,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6295,7 +6303,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6307,7 +6315,7 @@
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6316,7 +6324,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6327,10 +6335,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6353,19 +6361,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6390,13 +6398,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6414,7 +6422,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6426,7 +6434,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6435,21 +6443,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6475,23 +6483,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6533,7 +6541,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6545,7 +6553,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6554,21 +6562,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6594,13 +6602,13 @@
         <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6650,7 +6658,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6662,7 +6670,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6671,21 +6679,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6708,13 +6716,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6765,7 +6773,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6777,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6786,21 +6794,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6823,16 +6831,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6882,7 +6890,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6894,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6903,24 +6911,24 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -6945,13 +6953,13 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7033,7 +7041,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>167</v>
@@ -7148,7 +7156,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>174</v>
@@ -7245,7 +7253,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7265,10 +7273,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7294,16 +7302,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7328,13 +7336,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7352,7 +7360,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7364,7 +7372,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7373,7 +7381,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7384,10 +7392,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7410,19 +7418,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7447,13 +7455,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7471,7 +7479,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7483,7 +7491,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7492,21 +7500,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7532,23 +7540,23 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7590,7 +7598,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7602,7 +7610,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7611,21 +7619,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7651,13 +7659,13 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7707,7 +7715,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7719,7 +7727,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7728,21 +7736,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7765,13 +7773,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7822,7 +7830,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7834,7 +7842,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7843,21 +7851,21 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7880,16 +7888,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7939,7 +7947,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7951,7 +7959,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7960,21 +7968,21 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8000,13 +8008,13 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,13 +8040,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8056,7 +8064,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8071,16 +8079,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8088,10 +8096,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8114,16 +8122,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8149,13 +8157,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8173,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8188,13 +8196,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8213,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8234,13 +8242,13 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8266,13 +8274,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8290,7 +8298,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8305,16 +8313,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8330,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8348,16 +8356,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8387,7 +8395,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8405,7 +8413,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8423,13 +8431,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8437,10 +8445,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8466,13 +8474,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8498,13 +8506,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8522,7 +8530,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8537,16 +8545,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8554,10 +8562,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8580,16 +8588,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8639,7 +8647,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8660,7 +8668,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8679,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8697,13 +8705,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8754,7 +8762,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8775,7 +8783,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8786,10 +8794,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8812,16 +8820,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8850,10 +8858,10 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8871,7 +8879,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8886,27 +8894,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8929,16 +8937,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8988,7 +8996,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9003,27 +9011,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9046,16 +9054,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9105,7 +9113,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9120,27 +9128,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9163,16 +9171,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9222,7 +9230,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9237,16 +9245,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9262,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9280,13 +9288,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9337,7 +9345,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9352,27 +9360,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9395,16 +9403,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9454,7 +9462,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9469,16 +9477,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9486,10 +9494,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9512,16 +9520,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9571,7 +9579,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9586,16 +9594,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9611,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9629,16 +9637,16 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9664,11 +9672,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9686,7 +9694,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9701,13 +9709,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9726,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9744,16 +9752,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9803,7 +9811,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9824,10 +9832,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9835,10 +9843,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9861,16 +9869,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9896,13 +9904,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9920,7 +9928,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9935,27 +9943,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,16 +9986,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10037,7 +10045,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10052,16 +10060,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10069,10 +10077,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10095,16 +10103,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10154,7 +10162,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10169,13 +10177,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10186,10 +10194,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10215,13 +10223,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10271,7 +10279,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10292,7 +10300,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10311,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10329,16 +10337,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10388,7 +10396,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10403,13 +10411,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10420,10 +10428,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10449,14 +10457,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10505,7 +10513,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,13 +10528,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10537,10 +10545,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,16 +10571,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10598,13 +10606,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10622,7 +10630,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10643,7 +10651,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10662,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10680,16 +10688,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10739,7 +10747,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10762,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10771,10 +10779,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10797,16 +10805,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10856,7 +10864,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10871,13 +10879,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10896,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10914,16 +10922,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10973,7 +10981,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10985,7 +10993,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -10994,7 +11002,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11005,10 +11013,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11031,13 +11039,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11088,7 +11096,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11106,10 +11114,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11120,10 +11128,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11149,10 +11157,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11235,10 +11243,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11264,10 +11272,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11348,13 +11356,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11376,13 +11384,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11442,10 +11450,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11465,13 +11473,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11493,13 +11501,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11559,10 +11567,10 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11582,14 +11590,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11611,10 +11619,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11669,7 +11677,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11701,10 +11709,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11727,16 +11735,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11786,7 +11794,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11807,7 +11815,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11826,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11933,10 +11941,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12050,14 +12058,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12079,10 +12087,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12137,7 +12145,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12177,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,16 +12203,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12254,7 +12262,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12263,10 +12271,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12275,21 +12283,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12312,16 +12320,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12371,7 +12379,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12392,7 +12400,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12403,10 +12411,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12429,16 +12437,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12488,7 +12496,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12509,7 +12517,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12520,10 +12528,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12546,19 +12554,19 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12607,7 +12615,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12625,10 +12633,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12639,10 +12647,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12754,10 +12762,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12851,7 +12859,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12871,10 +12879,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12897,16 +12905,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12956,7 +12964,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12965,10 +12973,10 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12977,21 +12985,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13014,23 +13022,23 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
@@ -13075,7 +13083,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13084,10 +13092,10 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13096,21 +13104,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13133,16 +13141,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13192,7 +13200,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13210,24 +13218,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,16 +13258,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13309,7 +13317,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13318,10 +13326,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13330,21 +13338,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13367,16 +13375,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,7 +13434,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13444,10 +13452,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13466,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13573,10 +13581,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13670,7 +13678,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13690,10 +13698,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13716,19 +13724,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13777,7 +13785,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13789,7 +13797,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13798,21 +13806,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13838,20 +13846,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13872,13 +13880,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13896,7 +13904,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13908,7 +13916,7 @@
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -13917,21 +13925,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13957,21 +13965,21 @@
         <v>168</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14013,7 +14021,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14025,7 +14033,7 @@
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14034,21 +14042,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14074,21 +14082,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14130,7 +14138,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14139,10 +14147,10 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14151,21 +14159,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14191,23 +14199,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14249,7 +14257,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14261,7 +14269,7 @@
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14270,21 +14278,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14307,16 +14315,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14366,7 +14374,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14387,10 +14395,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14398,10 +14406,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14424,13 +14432,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14481,7 +14489,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14499,10 +14507,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14513,10 +14521,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14628,10 +14636,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14745,14 +14753,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14774,10 +14782,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14832,7 +14840,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14864,10 +14872,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14890,16 +14898,16 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14929,7 +14937,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14947,7 +14955,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14965,24 +14973,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15005,16 +15013,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15040,13 +15048,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15064,7 +15072,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15082,24 +15090,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15122,16 +15130,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15181,7 +15189,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15196,13 +15204,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15213,14 +15221,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15239,16 +15247,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15298,7 +15306,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15319,7 +15327,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15330,10 +15338,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,16 +15364,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15415,7 +15423,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15430,13 +15438,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
   <si>
     <t>Property</t>
   </si>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -575,10 +575,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>MedicationRequest.identifier:rpNumber.use</t>
   </si>
   <si>
@@ -607,10 +603,6 @@
   </si>
   <si>
     <t>Identifier.use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
   </si>
   <si>
     <t>Role.code or implied by context</t>
@@ -826,7 +818,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
@@ -4082,7 +4074,7 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>82</v>
@@ -4102,10 +4094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4131,16 +4123,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4165,52 +4157,52 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4221,10 +4213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4247,19 +4239,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4284,66 +4276,66 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4369,100 +4361,100 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="S17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4488,13 +4480,13 @@
         <v>168</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4544,42 +4536,42 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4602,13 +4594,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4659,42 +4651,42 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4717,16 +4709,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4776,45 +4768,45 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4839,13 +4831,13 @@
         <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4927,7 +4919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>167</v>
@@ -5042,7 +5034,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>174</v>
@@ -5139,7 +5131,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5159,10 +5151,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5188,16 +5180,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5222,52 +5214,52 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y24" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y24" t="s" s="2">
+      <c r="Z24" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Z24" t="s" s="2">
+      <c r="AA24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AA24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF24" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5278,10 +5270,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5304,19 +5296,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5341,66 +5333,66 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5426,23 +5418,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5484,42 +5476,42 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5545,13 +5537,13 @@
         <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5601,42 +5593,42 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5659,13 +5651,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5716,42 +5708,42 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5774,16 +5766,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5833,45 +5825,45 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5896,13 +5888,13 @@
         <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5984,7 +5976,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>167</v>
@@ -6099,7 +6091,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>174</v>
@@ -6196,7 +6188,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6216,10 +6208,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6245,16 +6237,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6279,52 +6271,52 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y33" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Z33" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Z33" t="s" s="2">
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6335,10 +6327,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6361,19 +6353,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6398,66 +6390,66 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z34" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z34" t="s" s="2">
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6483,23 +6475,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6541,42 +6533,42 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6602,13 +6594,13 @@
         <v>168</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6658,42 +6650,42 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6716,13 +6708,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6773,42 +6765,42 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6831,16 +6823,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6890,45 +6882,45 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -6953,13 +6945,13 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7041,7 +7033,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>167</v>
@@ -7156,7 +7148,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>174</v>
@@ -7253,7 +7245,7 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7273,10 +7265,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7302,16 +7294,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7336,52 +7328,52 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y42" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="Y42" t="s" s="2">
+      <c r="Z42" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="Z42" t="s" s="2">
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AA42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF42" t="s" s="2">
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7392,10 +7384,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7418,19 +7410,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7455,66 +7447,66 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="Y43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7540,23 +7532,23 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7598,42 +7590,42 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7659,13 +7651,13 @@
         <v>168</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7715,42 +7707,42 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7773,13 +7765,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7830,42 +7822,42 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7888,16 +7880,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7947,42 +7939,42 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8008,13 +8000,13 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8040,13 +8032,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8064,7 +8056,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8079,16 +8071,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AL48" t="s" s="2">
+      <c r="AN48" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8096,10 +8088,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8122,16 +8114,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8157,14 +8149,14 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Y49" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8181,7 +8173,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8196,13 +8188,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8213,10 +8205,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8242,13 +8234,13 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8274,13 +8266,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8298,7 +8290,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8313,16 +8305,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8330,10 +8322,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8356,16 +8348,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8395,7 +8387,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8413,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8431,13 +8423,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8445,10 +8437,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8474,13 +8466,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8506,13 +8498,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8530,7 +8522,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8545,16 +8537,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8562,10 +8554,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8588,16 +8580,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8647,7 +8639,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8668,7 +8660,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8679,10 +8671,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8705,13 +8697,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8762,7 +8754,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8783,7 +8775,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8794,10 +8786,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,16 +8812,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8858,10 +8850,10 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8879,7 +8871,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8894,27 +8886,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8937,16 +8929,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8996,7 +8988,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9011,27 +9003,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>363</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9054,16 +9046,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9113,7 +9105,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9128,27 +9120,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9171,16 +9163,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9230,7 +9222,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9245,16 +9237,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9262,10 +9254,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9288,13 +9280,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9345,7 +9337,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9360,27 +9352,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9403,16 +9395,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9462,7 +9454,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9477,16 +9469,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9494,10 +9486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9520,16 +9512,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9579,7 +9571,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9594,16 +9586,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9611,10 +9603,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9637,16 +9629,16 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9672,11 +9664,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9694,7 +9686,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9709,13 +9701,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9726,10 +9718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9752,16 +9744,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9811,7 +9803,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9832,10 +9824,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9843,10 +9835,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9869,16 +9861,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9904,13 +9896,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9928,7 +9920,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9943,27 +9935,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>425</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9986,16 +9978,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10045,7 +10037,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10060,16 +10052,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10077,10 +10069,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10103,16 +10095,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10162,7 +10154,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10177,13 +10169,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10194,10 +10186,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10223,13 +10215,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10279,7 +10271,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10300,7 +10292,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10311,10 +10303,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10337,16 +10329,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L68" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>446</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10396,7 +10388,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10411,13 +10403,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10428,10 +10420,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10457,14 +10449,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10513,7 +10505,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10528,13 +10520,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10545,10 +10537,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10571,16 +10563,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10606,13 +10598,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10630,7 +10622,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10651,7 +10643,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10662,10 +10654,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10688,16 +10680,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L71" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10747,7 +10739,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10762,13 +10754,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10779,10 +10771,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10805,16 +10797,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10864,7 +10856,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10879,13 +10871,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10896,10 +10888,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10922,16 +10914,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N73" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10981,7 +10973,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10993,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11002,7 +10994,7 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11013,10 +11005,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11039,13 +11031,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11096,7 +11088,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11114,10 +11106,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11128,10 +11120,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11157,10 +11149,10 @@
         <v>168</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11243,10 +11235,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11272,10 +11264,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11356,13 +11348,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11384,13 +11376,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11450,10 +11442,10 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11473,13 +11465,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11501,13 +11493,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11567,10 +11559,10 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11590,14 +11582,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11619,10 +11611,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11677,7 +11669,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11709,10 +11701,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11735,16 +11727,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N80" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11794,7 +11786,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11815,7 +11807,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11826,10 +11818,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11941,10 +11933,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12058,14 +12050,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12087,10 +12079,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12145,7 +12137,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12177,10 +12169,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12203,16 +12195,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12262,7 +12254,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12271,33 +12263,33 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AJ84" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12320,16 +12312,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L85" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>528</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12379,7 +12371,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12400,7 +12392,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12411,10 +12403,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12437,16 +12429,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12496,7 +12488,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12517,7 +12509,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12528,10 +12520,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12554,19 +12546,19 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N87" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12615,7 +12607,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12633,10 +12625,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12647,10 +12639,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12762,10 +12754,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12859,7 +12851,7 @@
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12879,10 +12871,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12905,16 +12897,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12964,42 +12956,42 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>549</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13022,103 +13014,103 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM91" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13141,16 +13133,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13200,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13218,24 +13210,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>565</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13258,16 +13250,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13317,7 +13309,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13326,33 +13318,33 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AJ93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>524</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13375,16 +13367,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13434,7 +13426,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13452,10 +13444,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13466,10 +13458,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13581,10 +13573,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13678,7 +13670,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13698,10 +13690,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13724,19 +13716,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13785,42 +13777,42 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>585</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13846,100 +13838,100 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y98" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
+      <c r="Z98" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="R98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM98" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>595</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13965,98 +13957,98 @@
         <v>168</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>603</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14082,98 +14074,98 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AJ100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14199,100 +14191,100 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM101" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14315,16 +14307,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="L102" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>623</v>
-      </c>
       <c r="N102" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14374,7 +14366,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14395,10 +14387,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14406,10 +14398,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14432,13 +14424,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14489,7 +14481,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14507,10 +14499,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14521,10 +14513,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14636,10 +14628,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14753,14 +14745,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14782,10 +14774,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14840,7 +14832,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14872,10 +14864,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14898,16 +14890,16 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14937,7 +14929,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14955,7 +14947,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14973,24 +14965,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15013,16 +15005,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>642</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15048,13 +15040,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15072,7 +15064,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15090,24 +15082,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>645</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15130,16 +15122,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L109" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15189,7 +15181,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15204,13 +15196,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15221,14 +15213,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15247,16 +15239,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>659</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15306,7 +15298,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15327,7 +15319,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15338,10 +15330,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15364,16 +15356,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15423,7 +15415,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15438,13 +15430,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -806,6 +806,63 @@
     <t>MedicationRequest.identifier:orderInRp.assigner</t>
   </si>
   <si>
+    <t>MedicationRequest.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
     <t>MedicationRequest.identifier:requestIdentifierCommon</t>
   </si>
   <si>
@@ -815,91 +872,73 @@
     <t>処方箋に対するID</t>
   </si>
   <si>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution</t>
+  </si>
+  <si>
+    <t>requestIdentifierInstitution</t>
+  </si>
+  <si>
+    <t>医療機関毎に管理される処方箋に対するID</t>
+  </si>
+  <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>identifier値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.11</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.system</t>
+  </si>
+  <si>
+    <t>保険医療機関番号を含む処方箋IDのSystem値（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifierInstitution.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2405,12 +2444,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.58984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5873,7 +5912,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6930,7 +6969,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -7974,15 +8013,17 @@
         <v>287</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -7991,22 +8032,22 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,13 +8073,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8056,13 +8097,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>148</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8071,27 +8112,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>293</v>
+        <v>156</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>294</v>
+        <v>157</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>297</v>
+        <v>167</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8114,17 +8155,15 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>298</v>
+        <v>169</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8149,13 +8188,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8173,7 +8212,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8185,16 +8224,16 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>172</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8205,42 +8244,42 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>174</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>175</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8266,55 +8305,55 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>309</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>178</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>312</v>
+        <v>172</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8361,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>180</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8336,30 +8375,32 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>181</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>182</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8383,11 +8424,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>318</v>
+        <v>187</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8405,13 +8448,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8423,24 +8466,24 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>320</v>
+        <v>189</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>191</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8463,18 +8506,20 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8498,13 +8543,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>198</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>199</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8522,7 +8567,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8537,27 +8582,27 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>189</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>203</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8574,24 +8619,26 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8639,7 +8686,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>209</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8660,21 +8707,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>210</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>211</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>297</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>213</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8682,7 +8729,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
@@ -8697,15 +8744,17 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>337</v>
+        <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>269</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8754,7 +8803,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>217</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8775,21 +8824,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>218</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>221</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8797,7 +8846,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8812,17 +8861,15 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>223</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8847,13 +8894,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8871,10 +8918,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8886,27 +8933,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>349</v>
+        <v>226</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>229</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8914,7 +8961,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>91</v>
@@ -8929,16 +8976,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>231</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>232</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>356</v>
+        <v>233</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8988,10 +9035,10 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>234</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>91</v>
@@ -9003,27 +9050,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>359</v>
+        <v>235</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>361</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9031,7 +9078,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
@@ -9040,22 +9087,22 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>363</v>
+        <v>111</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>301</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>302</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>303</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9081,13 +9128,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9105,10 +9152,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -9120,27 +9167,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>367</v>
+        <v>306</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>368</v>
+        <v>308</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9151,7 +9198,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9163,16 +9210,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>372</v>
+        <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>311</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>375</v>
+        <v>312</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9198,13 +9245,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9222,13 +9269,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9237,16 +9284,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>317</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9301,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9274,21 +9321,23 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>319</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9313,13 +9362,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9337,10 +9386,10 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>91</v>
@@ -9352,27 +9401,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>382</v>
+        <v>324</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>386</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9383,7 +9432,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9392,19 +9441,19 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>388</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>328</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
+        <v>329</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9430,13 +9479,11 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9454,13 +9501,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>327</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9469,16 +9516,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>326</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9486,10 +9533,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9509,19 +9556,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>394</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>337</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9547,13 +9594,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9571,7 +9618,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9586,16 +9633,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>397</v>
+        <v>340</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>398</v>
+        <v>341</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9650,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9623,22 +9670,22 @@
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>344</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>345</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>403</v>
+        <v>347</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9664,11 +9711,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9686,7 +9735,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>343</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9701,13 +9750,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>348</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9767,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9741,20 +9790,18 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>351</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9803,7 +9850,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>349</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9824,10 +9871,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>353</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9835,10 +9882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9846,10 +9893,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9858,19 +9905,19 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>355</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9896,13 +9943,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>417</v>
+        <v>358</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>418</v>
+        <v>359</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9920,13 +9967,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>354</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9935,27 +9982,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>360</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>361</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>362</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>363</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>423</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9963,10 +10010,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -9975,19 +10022,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>425</v>
+        <v>366</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>367</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
+        <v>368</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>428</v>
+        <v>369</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10037,13 +10084,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10052,27 +10099,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>429</v>
+        <v>370</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>294</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>430</v>
+        <v>372</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>422</v>
+        <v>373</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10083,7 +10130,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10092,19 +10139,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>378</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>435</v>
+        <v>379</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10154,13 +10201,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
@@ -10169,27 +10216,27 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>380</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>437</v>
+        <v>381</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10209,19 +10256,19 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>385</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>386</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
+        <v>388</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10271,7 +10318,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>384</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10286,16 +10333,16 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>390</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10314,10 +10361,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10329,17 +10376,15 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>392</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10388,13 +10433,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>391</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10403,27 +10448,27 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>446</v>
+        <v>397</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10446,18 +10491,18 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>401</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10505,7 +10550,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>400</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,16 +10565,16 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>451</v>
+        <v>404</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>452</v>
+        <v>372</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10537,10 +10582,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,16 +10608,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>192</v>
+        <v>407</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>408</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>409</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>388</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10598,13 +10643,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10622,7 +10667,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>406</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10637,16 +10682,16 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>459</v>
+        <v>411</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10699,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10668,7 +10713,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10677,19 +10722,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>414</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10715,13 +10760,11 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10739,13 +10782,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10754,13 +10797,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>465</v>
+        <v>419</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10771,10 +10814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10785,7 +10828,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10797,16 +10840,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>421</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>422</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>423</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>470</v>
+        <v>388</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10856,13 +10899,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -10871,16 +10914,16 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>473</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10931,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10914,16 +10957,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>427</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>477</v>
+        <v>429</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10949,13 +10992,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>82</v>
+        <v>430</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -10973,7 +11016,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>426</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10988,27 +11031,27 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11019,7 +11062,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11031,15 +11074,17 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>480</v>
+        <v>438</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>439</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11088,13 +11133,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11103,16 +11148,16 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>307</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11120,10 +11165,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11134,7 +11179,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11143,18 +11188,20 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>445</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>446</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11203,28 +11250,28 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>171</v>
+        <v>444</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>172</v>
+        <v>450</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11235,10 +11282,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11258,18 +11305,20 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11306,17 +11355,19 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>178</v>
+        <v>451</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11328,7 +11379,7 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11337,7 +11388,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11348,14 +11399,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>454</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11373,18 +11422,20 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>455</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11433,7 +11484,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>178</v>
+        <v>454</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11442,19 +11493,19 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11465,14 +11516,12 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11490,19 +11539,21 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>461</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>462</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11550,28 +11601,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>178</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11582,46 +11633,44 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>466</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>504</v>
+        <v>467</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>505</v>
+        <v>468</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11645,13 +11694,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>82</v>
+        <v>470</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>471</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11669,19 +11718,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>466</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11690,7 +11739,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>134</v>
+        <v>472</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11701,10 +11750,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11715,7 +11764,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11727,16 +11776,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>508</v>
+        <v>475</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>510</v>
+        <v>388</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11786,13 +11835,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -11801,13 +11850,13 @@
         <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11867,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11832,7 +11881,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11844,15 +11893,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>168</v>
+        <v>480</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>169</v>
+        <v>481</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11901,28 +11952,28 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>171</v>
+        <v>479</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>172</v>
+        <v>486</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11933,14 +11984,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11959,16 +12010,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>488</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>138</v>
+        <v>489</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
+        <v>489</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>140</v>
+        <v>490</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12018,7 +12069,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>178</v>
+        <v>487</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12030,7 +12081,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12039,7 +12090,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>172</v>
+        <v>491</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12050,46 +12101,42 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>137</v>
+        <v>493</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12137,28 +12184,28 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>134</v>
+        <v>497</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12169,10 +12216,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,17 +12242,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>168</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12254,7 +12299,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>171</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12263,10 +12308,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12275,21 +12320,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>521</v>
+        <v>172</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12300,7 +12345,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12312,17 +12357,15 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>524</v>
+        <v>137</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12359,31 +12402,29 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>178</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12392,7 +12433,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12403,12 +12444,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12417,7 +12460,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12429,17 +12472,15 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12488,19 +12529,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>178</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12509,7 +12550,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12520,12 +12561,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12546,20 +12589,16 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>222</v>
+        <v>512</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12607,28 +12646,28 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>178</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12639,42 +12678,46 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>515</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>169</v>
+        <v>517</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12722,19 +12765,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>171</v>
+        <v>519</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12743,7 +12786,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12754,21 +12797,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12780,16 +12823,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>137</v>
+        <v>493</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>138</v>
+        <v>521</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>175</v>
+        <v>522</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>140</v>
+        <v>523</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12827,31 +12870,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>178</v>
+        <v>520</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12860,7 +12903,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>172</v>
+        <v>524</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12871,10 +12914,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12894,20 +12937,18 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>541</v>
+        <v>169</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -12956,7 +12997,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>171</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12965,10 +13006,10 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -12977,32 +13018,32 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>172</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13011,27 +13052,25 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>137</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>549</v>
+        <v>138</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>550</v>
+        <v>175</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>551</v>
+        <v>140</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>552</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13075,19 +13114,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>178</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13096,55 +13135,57 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>172</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>527</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>557</v>
+        <v>137</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>517</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>518</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13192,42 +13233,42 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>519</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>561</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>562</v>
+        <v>134</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,16 +13291,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>530</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13309,7 +13350,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>528</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13318,10 +13359,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13330,21 +13371,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>522</v>
+        <v>535</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13367,16 +13408,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>539</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,7 +13467,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13444,10 +13485,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>571</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>572</v>
+        <v>540</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13499,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>541</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13484,15 +13525,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>168</v>
+        <v>537</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>542</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13541,7 +13584,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>171</v>
+        <v>541</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13553,7 +13596,7 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13562,7 +13605,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>172</v>
+        <v>540</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13573,21 +13616,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>544</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13599,18 +13642,20 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>138</v>
+        <v>545</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>175</v>
+        <v>546</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13646,40 +13691,40 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>178</v>
+        <v>544</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>172</v>
+        <v>550</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13690,10 +13735,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13713,23 +13758,19 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>168</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>169</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13777,7 +13818,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>581</v>
+        <v>171</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13789,7 +13830,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13798,61 +13839,59 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>582</v>
+        <v>172</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>583</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>585</v>
+        <v>138</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q98" t="s" s="2">
-        <v>588</v>
-      </c>
+      <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13872,43 +13911,43 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>589</v>
+        <v>82</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>591</v>
+        <v>178</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -13917,21 +13956,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>592</v>
+        <v>172</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>594</v>
+        <v>553</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>594</v>
+        <v>553</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13954,24 +13993,24 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>168</v>
+        <v>392</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>595</v>
+        <v>554</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14013,7 +14052,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14022,7 +14061,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14034,21 +14073,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>600</v>
+        <v>559</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>601</v>
+        <v>560</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>561</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>561</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14071,24 +14110,26 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>603</v>
+        <v>562</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="R100" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14130,7 +14171,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>607</v>
+        <v>566</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14139,7 +14180,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>608</v>
+        <v>558</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14151,21 +14192,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>567</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>601</v>
+        <v>568</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14185,29 +14226,27 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>570</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>611</v>
+        <v>571</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>612</v>
+        <v>572</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>614</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>615</v>
+        <v>82</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14249,7 +14288,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>569</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14267,24 +14306,24 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>617</v>
+        <v>575</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>577</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>577</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14307,16 +14346,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>619</v>
+        <v>529</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>578</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>579</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>375</v>
+        <v>532</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14366,7 +14405,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>618</v>
+        <v>577</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14375,10 +14414,10 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>103</v>
+        <v>533</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14387,21 +14426,21 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>580</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>623</v>
+        <v>580</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14424,15 +14463,17 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>624</v>
+        <v>581</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14481,7 +14522,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>623</v>
+        <v>580</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14499,10 +14540,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>626</v>
+        <v>584</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>627</v>
+        <v>585</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14513,10 +14554,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>628</v>
+        <v>586</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>628</v>
+        <v>586</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14628,10 +14669,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>587</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14701,16 +14742,16 @@
         <v>82</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF105" t="s" s="2">
         <v>178</v>
@@ -14745,45 +14786,45 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>630</v>
+        <v>588</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>630</v>
+        <v>588</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>137</v>
+        <v>589</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>504</v>
+        <v>590</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>505</v>
+        <v>591</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>140</v>
+        <v>592</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>146</v>
+        <v>593</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14832,19 +14873,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>506</v>
+        <v>594</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -14853,21 +14894,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>134</v>
+        <v>595</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>631</v>
+        <v>597</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>631</v>
+        <v>597</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14875,7 +14916,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>91</v>
@@ -14884,28 +14925,30 @@
         <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="R107" t="s" s="2">
         <v>82</v>
       </c>
@@ -14925,11 +14968,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>634</v>
+        <v>603</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14947,10 +14992,10 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>91</v>
@@ -14965,24 +15010,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>635</v>
+        <v>605</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>636</v>
+        <v>606</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>637</v>
+        <v>607</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15002,27 +15047,27 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>638</v>
+        <v>608</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>610</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>82</v>
@@ -15040,13 +15085,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>642</v>
+        <v>82</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15064,7 +15109,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>637</v>
+        <v>612</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15082,24 +15127,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>643</v>
+        <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>645</v>
+        <v>614</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>615</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>615</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15119,27 +15164,27 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>647</v>
+        <v>105</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>648</v>
+        <v>616</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>82</v>
@@ -15181,7 +15226,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>646</v>
+        <v>620</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15190,44 +15235,44 @@
         <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>643</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>651</v>
+        <v>622</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>652</v>
+        <v>623</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>652</v>
+        <v>623</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>653</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15236,27 +15281,29 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>654</v>
+        <v>111</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>656</v>
+        <v>625</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O110" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>82</v>
@@ -15298,13 +15345,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15319,21 +15366,21 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15344,7 +15391,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15356,16 +15403,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>660</v>
+        <v>632</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>663</v>
+        <v>388</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15415,13 +15462,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15430,18 +15477,1067 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y116" s="2"/>
+      <c r="Z116" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="AM118" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
+      <c r="AN118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
+      <c r="B119" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO120" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -494,7 +494,15 @@
 このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
-    <t>これは業務IDであって、リソースに対するIDではない。</t>
+    <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
+Slice定義は下記のようになる。  
+[Sliceで定義される識別子]  
+　- rpNumber : 処方箋内部の剤グループとしてのRp番号  
+　- orderInRp : 同一RP番号（剤グループ）での薬剤の表記順  
+　- requestIdentifier : 処方オーダに対するID  
+　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
+[invariantで定義される識別子]  
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -504,6 +512,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -863,10 +875,10 @@
     <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
     <t>処方箋に対するID</t>
@@ -875,70 +887,31 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.system</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution</t>
-  </si>
-  <si>
-    <t>requestIdentifierInstitution</t>
-  </si>
-  <si>
-    <t>医療機関毎に管理される処方箋に対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.system</t>
-  </si>
-  <si>
-    <t>保険医療機関番号を含む処方箋IDのSystem値（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierInstitution.assigner</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2444,12 +2417,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO120"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.58984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3762,33 +3735,33 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3813,13 +3786,13 @@
         <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3884,27 +3857,27 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3927,13 +3900,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3984,7 +3957,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -4005,7 +3978,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -4016,10 +3989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4048,7 +4021,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>140</v>
@@ -4089,10 +4062,10 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -4101,7 +4074,7 @@
         <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4122,7 +4095,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4133,10 +4106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4162,16 +4135,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4196,13 +4169,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4220,7 +4193,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4241,7 +4214,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4252,10 +4225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4278,19 +4251,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4315,13 +4288,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4339,7 +4312,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4360,21 +4333,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4400,23 +4373,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4458,7 +4431,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4479,21 +4452,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4516,16 +4489,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4575,7 +4548,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4596,21 +4569,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4633,13 +4606,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4690,7 +4663,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4711,21 +4684,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4748,16 +4721,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4807,7 +4780,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4828,24 +4801,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4870,13 +4843,13 @@
         <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4941,27 +4914,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4984,13 +4957,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5041,7 +5014,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5062,7 +5035,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5073,10 +5046,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5105,7 +5078,7 @@
         <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>140</v>
@@ -5146,10 +5119,10 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -5158,7 +5131,7 @@
         <v>155</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5179,7 +5152,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5190,10 +5163,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5219,16 +5192,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5253,13 +5226,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5277,7 +5250,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5298,7 +5271,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5309,10 +5282,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5335,19 +5308,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5372,13 +5345,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5396,7 +5369,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5417,21 +5390,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5457,23 +5430,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5515,7 +5488,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5536,21 +5509,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5573,16 +5546,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5632,7 +5605,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5653,21 +5626,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5690,13 +5663,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5747,7 +5720,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5768,21 +5741,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5805,16 +5778,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5864,7 +5837,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5885,24 +5858,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5927,13 +5900,13 @@
         <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5998,27 +5971,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6041,13 +6014,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6098,7 +6071,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6119,7 +6092,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6130,10 +6103,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6162,7 +6135,7 @@
         <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -6203,10 +6176,10 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6215,7 +6188,7 @@
         <v>155</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6236,7 +6209,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6247,10 +6220,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6276,16 +6249,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6310,13 +6283,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6334,7 +6307,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6355,7 +6328,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6366,10 +6339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6392,19 +6365,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6429,13 +6402,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6453,7 +6426,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6474,21 +6447,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6514,23 +6487,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6572,7 +6545,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6593,21 +6566,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6630,16 +6603,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6689,7 +6662,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6710,21 +6683,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6747,13 +6720,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6804,7 +6777,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6825,21 +6798,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6862,16 +6835,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6921,7 +6894,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6942,24 +6915,24 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -6984,13 +6957,13 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7055,27 +7028,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7098,13 +7071,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7155,7 +7128,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7176,7 +7149,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7187,10 +7160,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7219,7 +7192,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -7260,10 +7233,10 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
@@ -7272,7 +7245,7 @@
         <v>155</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7293,7 +7266,7 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -7304,10 +7277,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7333,16 +7306,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7367,13 +7340,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7391,7 +7364,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7412,7 +7385,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7423,10 +7396,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7449,19 +7422,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7486,13 +7459,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7510,7 +7483,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7531,21 +7504,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7571,23 +7544,23 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7629,7 +7602,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7650,21 +7623,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7687,16 +7660,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7746,7 +7719,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7767,21 +7740,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7804,13 +7777,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7861,7 +7834,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7882,21 +7855,21 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7919,16 +7892,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7978,7 +7951,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7999,31 +7972,29 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C48" t="s" s="2">
         <v>288</v>
       </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -8032,13 +8003,13 @@
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>289</v>
@@ -8047,7 +8018,7 @@
         <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8073,13 +8044,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8097,13 +8068,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8112,27 +8083,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>157</v>
+        <v>295</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>158</v>
+        <v>296</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>159</v>
+        <v>297</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>167</v>
+        <v>298</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8155,15 +8126,17 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>169</v>
+        <v>299</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8188,13 +8161,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8212,7 +8185,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>171</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8224,16 +8197,16 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>172</v>
+        <v>305</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8244,42 +8217,42 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>174</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>138</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>140</v>
+        <v>309</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8305,55 +8278,55 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>178</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>172</v>
+        <v>313</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8361,10 +8334,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>180</v>
+        <v>315</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8375,32 +8348,30 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>181</v>
+        <v>316</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>182</v>
+        <v>317</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8424,13 +8395,11 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>187</v>
+        <v>319</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8448,13 +8417,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>188</v>
+        <v>315</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8466,24 +8435,24 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>189</v>
+        <v>321</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>191</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8506,20 +8475,18 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>193</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8543,13 +8510,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>198</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>199</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8567,7 +8534,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>200</v>
+        <v>322</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8582,27 +8549,27 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>189</v>
+        <v>329</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>203</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8619,26 +8586,24 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>105</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8686,7 +8651,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8707,21 +8672,21 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>210</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>213</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8729,7 +8694,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>91</v>
@@ -8744,17 +8709,15 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>168</v>
+        <v>338</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8803,7 +8766,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>217</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8824,21 +8787,21 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>218</v>
+        <v>341</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>221</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8846,7 +8809,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8861,15 +8824,17 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8894,13 +8859,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8918,10 +8883,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>225</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8933,27 +8898,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>226</v>
+        <v>350</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>227</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>299</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>229</v>
+        <v>353</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8961,7 +8926,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>91</v>
@@ -8976,16 +8941,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>230</v>
+        <v>354</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>231</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>232</v>
+        <v>356</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>233</v>
+        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9035,10 +9000,10 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>234</v>
+        <v>353</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>91</v>
@@ -9050,27 +9015,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>236</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9078,7 +9043,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
@@ -9087,22 +9052,22 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>111</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9128,13 +9093,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9152,10 +9117,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -9167,27 +9132,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9198,7 +9163,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9210,16 +9175,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>192</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9245,13 +9210,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9269,13 +9234,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9284,16 +9249,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9301,10 +9266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9321,23 +9286,21 @@
         <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>111</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9362,13 +9325,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9386,10 +9349,10 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>91</v>
@@ -9401,27 +9364,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>324</v>
+        <v>383</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9432,7 +9395,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9441,19 +9404,19 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9479,11 +9442,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9501,13 +9466,13 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>82</v>
@@ -9516,16 +9481,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>326</v>
+        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9533,10 +9498,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9556,19 +9521,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>111</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>335</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>336</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>337</v>
+        <v>376</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9594,13 +9559,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9618,7 +9583,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9633,16 +9598,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>341</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>342</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9650,10 +9615,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9670,22 +9635,22 @@
         <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>344</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>402</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
+        <v>403</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>347</v>
+        <v>404</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9711,13 +9676,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9735,7 +9698,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9750,13 +9713,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>82</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>348</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9767,10 +9730,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9790,18 +9753,20 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>350</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9850,7 +9815,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>349</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9871,10 +9836,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9882,10 +9847,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9893,10 +9858,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9905,19 +9870,19 @@
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9943,13 +9908,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>115</v>
+        <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9967,13 +9932,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9982,27 +9947,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>364</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10010,10 +9975,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10022,19 +9987,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10084,13 +10049,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10099,27 +10064,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>372</v>
+        <v>431</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>373</v>
+        <v>423</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10130,7 +10095,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10139,19 +10104,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10201,13 +10166,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
@@ -10216,27 +10181,27 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10256,19 +10221,19 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10318,7 +10283,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>384</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10333,16 +10298,16 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10350,10 +10315,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10361,10 +10326,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10376,15 +10341,17 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>393</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10433,13 +10400,13 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
@@ -10448,27 +10415,27 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>395</v>
+        <v>446</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10491,18 +10458,18 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>401</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10550,7 +10517,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10565,16 +10532,16 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>372</v>
+        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10582,10 +10549,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10608,16 +10575,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>409</v>
+        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10643,13 +10610,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10667,7 +10634,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10682,16 +10649,16 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>411</v>
+        <v>460</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10699,10 +10666,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10713,7 +10680,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10722,19 +10689,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>192</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10760,11 +10727,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10782,13 +10751,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10797,13 +10766,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10814,10 +10783,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10828,7 +10797,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10840,16 +10809,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>423</v>
+        <v>470</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>388</v>
+        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10899,13 +10868,13 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>420</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
@@ -10914,16 +10883,16 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10931,10 +10900,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10957,16 +10926,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>192</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10992,13 +10961,13 @@
         <v>82</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -11016,7 +10985,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11031,27 +11000,27 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11062,7 +11031,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11074,17 +11043,15 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11133,13 +11100,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>437</v>
+        <v>480</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11148,16 +11115,16 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>307</v>
+        <v>484</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11165,10 +11132,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11179,7 +11146,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11188,20 +11155,18 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>445</v>
+        <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11250,28 +11215,28 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>444</v>
+        <v>172</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>450</v>
+        <v>173</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11282,10 +11247,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>451</v>
+        <v>489</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11305,20 +11270,18 @@
         <v>82</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>452</v>
+        <v>490</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11355,19 +11318,17 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>451</v>
+        <v>179</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11379,7 +11340,7 @@
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11388,7 +11349,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11399,12 +11360,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>454</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11422,20 +11385,18 @@
         <v>82</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>456</v>
+        <v>495</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11484,7 +11445,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>179</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11493,19 +11454,19 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>82</v>
@@ -11516,12 +11477,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11539,21 +11502,19 @@
         <v>82</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11601,28 +11562,28 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>179</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>464</v>
+        <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>82</v>
@@ -11633,44 +11594,46 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>467</v>
+        <v>505</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11694,13 +11657,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11718,19 +11681,19 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>82</v>
@@ -11739,7 +11702,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>472</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11750,10 +11713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11764,7 +11727,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11776,16 +11739,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>476</v>
+        <v>510</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>388</v>
+        <v>511</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11835,13 +11798,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -11850,13 +11813,13 @@
         <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11867,10 +11830,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11881,7 +11844,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11893,17 +11856,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>480</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>481</v>
+        <v>170</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11952,28 +11913,28 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>479</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>486</v>
+        <v>173</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11984,14 +11945,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12010,16 +11971,16 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>488</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>489</v>
+        <v>138</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>489</v>
+        <v>176</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12069,7 +12030,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>487</v>
+        <v>179</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12081,7 +12042,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12090,7 +12051,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>491</v>
+        <v>173</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12101,42 +12062,46 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>492</v>
+        <v>515</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>493</v>
+        <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12184,28 +12149,28 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>497</v>
+        <v>134</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12216,10 +12181,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12242,15 +12207,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>168</v>
+        <v>517</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12299,7 +12266,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>171</v>
+        <v>516</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12308,10 +12275,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12320,21 +12287,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>172</v>
+        <v>522</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12345,7 +12312,7 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12357,15 +12324,17 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>137</v>
+        <v>525</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>502</v>
+        <v>526</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12402,29 +12371,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>178</v>
+        <v>524</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12433,7 +12404,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12444,14 +12415,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>505</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12460,7 +12429,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12472,15 +12441,17 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12529,19 +12500,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>178</v>
+        <v>529</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12550,7 +12521,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12561,14 +12532,12 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>510</v>
+        <v>532</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C87" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12589,16 +12558,20 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>512</v>
+        <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>534</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12646,28 +12619,28 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>178</v>
+        <v>532</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12678,46 +12651,42 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>517</v>
+        <v>170</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12765,19 +12734,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>172</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -12786,7 +12755,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12797,21 +12766,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12823,16 +12792,16 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>493</v>
+        <v>137</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>521</v>
+        <v>138</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>522</v>
+        <v>176</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>523</v>
+        <v>140</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12870,31 +12839,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>520</v>
+        <v>179</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12903,7 +12872,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>524</v>
+        <v>173</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12914,10 +12883,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12937,18 +12906,20 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>168</v>
+        <v>380</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>169</v>
+        <v>542</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -12997,7 +12968,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>171</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13006,10 +12977,10 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13018,32 +12989,32 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>172</v>
+        <v>547</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
@@ -13052,25 +13023,27 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>138</v>
+        <v>550</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>175</v>
+        <v>551</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13114,19 +13087,19 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>178</v>
+        <v>554</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>82</v>
@@ -13135,57 +13108,55 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>172</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>137</v>
+        <v>558</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>517</v>
+        <v>559</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>518</v>
+        <v>560</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13233,42 +13204,42 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>134</v>
+        <v>563</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13291,16 +13262,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>531</v>
+        <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13350,7 +13321,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13359,10 +13330,10 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13371,21 +13342,21 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13408,16 +13379,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>538</v>
+        <v>569</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>539</v>
+        <v>570</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>532</v>
+        <v>571</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13467,7 +13438,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13485,10 +13456,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>572</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>540</v>
+        <v>573</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13499,10 +13470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>541</v>
+        <v>574</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>541</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13525,17 +13496,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>537</v>
+        <v>169</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>542</v>
+        <v>170</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13584,7 +13553,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>541</v>
+        <v>172</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13596,7 +13565,7 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13605,7 +13574,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>540</v>
+        <v>173</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13616,21 +13585,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13642,20 +13611,18 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>545</v>
+        <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>546</v>
+        <v>176</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>548</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13691,40 +13658,40 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>544</v>
+        <v>179</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>550</v>
+        <v>173</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13735,10 +13702,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>551</v>
+        <v>576</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13758,19 +13725,23 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>168</v>
+        <v>577</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>169</v>
+        <v>578</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13818,7 +13789,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>171</v>
+        <v>582</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13830,7 +13801,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13839,59 +13810,61 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>172</v>
+        <v>583</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>82</v>
+        <v>584</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>138</v>
+        <v>586</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13911,43 +13884,43 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>178</v>
+        <v>592</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -13956,21 +13929,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>172</v>
+        <v>593</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>553</v>
+        <v>595</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>553</v>
+        <v>595</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13993,24 +13966,24 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>392</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>554</v>
+        <v>596</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14052,7 +14025,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14061,7 +14034,7 @@
         <v>91</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>103</v>
@@ -14073,21 +14046,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>559</v>
+        <v>601</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>560</v>
+        <v>602</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>561</v>
+        <v>603</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>561</v>
+        <v>603</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14110,26 +14083,24 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>562</v>
+        <v>604</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q100" t="s" s="2">
-        <v>565</v>
-      </c>
+      <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14171,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>566</v>
+        <v>608</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14180,7 +14151,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>558</v>
+        <v>609</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14192,21 +14163,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>568</v>
+        <v>602</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14226,27 +14197,29 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>570</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14288,7 +14261,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14306,24 +14279,24 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>574</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>576</v>
+        <v>602</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14346,16 +14319,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>529</v>
+        <v>620</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>532</v>
+        <v>376</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14405,7 +14378,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14414,10 +14387,10 @@
         <v>91</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>533</v>
+        <v>103</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>82</v>
@@ -14426,21 +14399,21 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>534</v>
+        <v>623</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14463,17 +14436,15 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>537</v>
+        <v>481</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>581</v>
+        <v>625</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>626</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14522,7 +14493,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>580</v>
+        <v>624</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14540,10 +14511,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>584</v>
+        <v>627</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>585</v>
+        <v>628</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14554,10 +14525,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>586</v>
+        <v>629</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>586</v>
+        <v>629</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14580,13 +14551,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14637,7 +14608,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14658,7 +14629,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14669,10 +14640,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14701,7 +14672,7 @@
         <v>138</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>140</v>
@@ -14742,19 +14713,19 @@
         <v>82</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14775,7 +14746,7 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
@@ -14786,45 +14757,45 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>589</v>
+        <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>590</v>
+        <v>505</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>591</v>
+        <v>506</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>592</v>
+        <v>140</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>593</v>
+        <v>146</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -14873,19 +14844,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>594</v>
+        <v>507</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -14894,21 +14865,21 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>595</v>
+        <v>134</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>596</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14916,7 +14887,7 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>91</v>
@@ -14925,30 +14896,28 @@
         <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q107" t="s" s="2">
-        <v>601</v>
-      </c>
+      <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
         <v>82</v>
       </c>
@@ -14968,13 +14937,11 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>603</v>
+        <v>635</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14992,10 +14959,10 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>604</v>
+        <v>632</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>91</v>
@@ -15010,24 +14977,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>627</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>605</v>
+        <v>636</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>606</v>
+        <v>637</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>607</v>
+        <v>638</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15047,27 +15014,27 @@
         <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>608</v>
+        <v>639</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>611</v>
+        <v>82</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>82</v>
@@ -15085,13 +15052,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>82</v>
+        <v>642</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15109,7 +15076,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15127,24 +15094,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>614</v>
+        <v>646</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15164,27 +15131,27 @@
         <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>105</v>
+        <v>648</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>616</v>
+        <v>649</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>619</v>
+        <v>82</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>82</v>
@@ -15226,7 +15193,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15235,44 +15202,44 @@
         <v>91</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15281,29 +15248,27 @@
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>111</v>
+        <v>655</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>625</v>
+        <v>657</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>627</v>
-      </c>
+        <v>658</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>82</v>
@@ -15345,13 +15310,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>629</v>
+        <v>653</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15366,21 +15331,21 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>630</v>
+        <v>659</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15391,7 +15356,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15403,16 +15368,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>633</v>
+        <v>662</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>634</v>
+        <v>663</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>388</v>
+        <v>664</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15462,13 +15427,13 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>631</v>
+        <v>660</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
@@ -15477,1067 +15442,18 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y116" s="2"/>
-      <c r="Z116" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -1526,13 +1526,19 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>薬をどのように服用すべきか / How the medication should be taken</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>薬の要求には、経口投与または静脈内または筋肉内の用量のオプションが含まれる場合があります。たとえば、「吐き気に必要に応じて、1日に2回Ondansetron 8mgまたはIV」または「Compazine®（プロクロロペラジン）5-10mg POまたは25mg PR BID PRN吐き気または嘔吐」。これらの場合、グループ化できる2つの投薬要求が作成されます。使用する投与経路の決定は、用量が必要な時点での患者の状態に基づいています。 / There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1666,14 +1672,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
@@ -1809,6 +1808,15 @@
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -10932,10 +10940,10 @@
         <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11000,13 +11008,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11017,10 +11025,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11043,13 +11051,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11100,7 +11108,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11118,10 +11126,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11132,10 +11140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11161,10 +11169,10 @@
         <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11247,10 +11255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11276,10 +11284,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11360,13 +11368,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11388,13 +11396,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11454,7 +11462,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11477,13 +11485,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11505,13 +11513,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11571,7 +11579,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11594,14 +11602,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11623,10 +11631,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11681,7 +11689,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11713,10 +11721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11739,16 +11747,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11798,7 +11806,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11819,7 +11827,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11830,10 +11838,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11945,10 +11953,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12062,14 +12070,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12091,10 +12099,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12149,7 +12157,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12181,10 +12189,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12207,16 +12215,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12266,7 +12274,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12275,10 +12283,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12287,13 +12295,13 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
@@ -12333,7 +12341,7 @@
         <v>527</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12450,7 +12458,7 @@
         <v>531</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13262,7 +13270,7 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>566</v>
@@ -13271,7 +13279,7 @@
         <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13330,33 +13338,33 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>497</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>521</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>522</v>
+        <v>569</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>523</v>
+        <v>570</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13382,13 +13390,13 @@
         <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13438,7 +13446,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13456,10 +13464,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13470,10 +13478,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13585,10 +13593,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13702,10 +13710,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13728,19 +13736,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13789,7 +13797,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13810,21 +13818,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13850,20 +13858,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13887,10 +13895,10 @@
         <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13908,7 +13916,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13929,21 +13937,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13969,21 +13977,21 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14025,7 +14033,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14046,21 +14054,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14086,21 +14094,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14142,7 +14150,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14151,7 +14159,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14163,21 +14171,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14203,23 +14211,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14261,7 +14269,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14282,21 +14290,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14319,13 +14327,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>376</v>
@@ -14378,7 +14386,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14399,7 +14407,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>413</v>
@@ -14410,10 +14418,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14436,13 +14444,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14493,7 +14501,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14511,10 +14519,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14525,10 +14533,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14640,10 +14648,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14757,14 +14765,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14786,10 +14794,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14844,7 +14852,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14876,10 +14884,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14905,13 +14913,13 @@
         <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14941,25 +14949,25 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14977,24 +14985,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15020,13 +15028,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15055,10 +15063,10 @@
         <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15076,7 +15084,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15094,24 +15102,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15134,13 +15142,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>376</v>
@@ -15193,7 +15201,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15208,13 +15216,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15225,14 +15233,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15251,16 +15259,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15310,7 +15318,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15331,7 +15339,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15342,10 +15350,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15368,16 +15376,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15427,7 +15435,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15442,13 +15450,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -1874,7 +1874,7 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1886,7 +1886,7 @@
     <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -881,7 +881,7 @@
     <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
-    <t>処方箋に対するID</t>
+    <t>全国で⼀意となる処方箋ID</t>
   </si>
   <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -1074,8 +1074,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1099,7 +1099,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1226,7 +1226,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1420,7 +1420,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1501,7 +1501,7 @@
 </t>
   </si>
   <si>
-    <t>薬剤単位の備考</t>
+    <t>薬剤オーダごとの備考</t>
   </si>
   <si>
     <t>他の属性では伝えることができなかったMedicationRequestについての付加的情報。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="671">
   <si>
     <t>Property</t>
   </si>
@@ -1804,12 +1804,15 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>調剤量</t>
+    <t>払い出される薬剤量</t>
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
   </si>
   <si>
+    <t>調剤後に払い出されるべき薬剤の量である。1日3錠、7日分という指示であれば21錠が払い出されるべき量である</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
   </si>
   <si>
@@ -1822,13 +1825,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
   </si>
   <si>
-    <t>調剤日数</t>
-  </si>
-  <si>
-    <t>供給される製品が使用されるか、あるいは払い出しが想定されている時間を指定する期間。</t>
-  </si>
-  <si>
-    <t>状況によっては、この属性は物理的に供給される量というよりも、想定されている期間に供給される薬剤の量を指定する数量の代わりに使われることもある。たとえば、薬剤が90日間供給される（オーダされた量に基づいて）など。可能であれば、量も示した方がより正確になる。expectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
+    <t>想定された使用期間</t>
+  </si>
+  <si>
+    <t>提供する薬剤が使用されることを想定した使用期間。</t>
+  </si>
+  <si>
+    <t>状況によっては、薬剤が供給される量として、物理的に供給される薬剤の錠数などの物理的量よりも、想定されている供給期間を使って表現されることもある。たとえば、薬剤を90日分提供する（オーダされた量に基づいて）など。可能であれば、量も示した方がより正確になる。ただし、実際には飲み忘れや紛失もあるためexpectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -13279,7 +13282,7 @@
         <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13347,24 +13350,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13390,13 +13393,13 @@
         <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13446,7 +13449,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13464,10 +13467,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13478,10 +13481,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,10 +13596,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13710,10 +13713,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13736,19 +13739,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13797,7 +13800,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13818,21 +13821,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13858,20 +13861,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13895,10 +13898,10 @@
         <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13916,7 +13919,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13937,21 +13940,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13977,21 +13980,21 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14033,7 +14036,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14054,21 +14057,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14094,21 +14097,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14150,7 +14153,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14159,7 +14162,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14171,21 +14174,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14211,23 +14214,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14269,7 +14272,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14290,21 +14293,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14327,13 +14330,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>376</v>
@@ -14386,7 +14389,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14407,7 +14410,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>413</v>
@@ -14418,10 +14421,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14447,10 +14450,10 @@
         <v>483</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14501,7 +14504,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14519,10 +14522,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14533,10 +14536,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14648,10 +14651,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14765,10 +14768,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14884,10 +14887,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14913,13 +14916,13 @@
         <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14949,7 +14952,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14967,7 +14970,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14985,24 +14988,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15028,13 +15031,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15063,10 +15066,10 @@
         <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15084,7 +15087,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15102,24 +15105,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15142,13 +15145,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>376</v>
@@ -15201,7 +15204,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15216,13 +15219,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15233,14 +15236,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15259,16 +15262,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15318,7 +15321,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15339,7 +15342,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15350,10 +15353,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15376,16 +15379,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15435,7 +15438,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15450,13 +15453,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -1825,13 +1825,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
   </si>
   <si>
-    <t>想定された使用期間</t>
-  </si>
-  <si>
-    <t>提供する薬剤が使用されることを想定した使用期間。</t>
-  </si>
-  <si>
-    <t>状況によっては、薬剤が供給される量として、物理的に供給される薬剤の錠数などの物理的量よりも、想定されている供給期間を使って表現されることもある。たとえば、薬剤を90日分提供する（オーダされた量に基づいて）など。可能であれば、量も示した方がより正確になる。ただし、実際には飲み忘れや紛失もあるためexpectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
+    <t>払い出される薬剤が想定された使用期間</t>
+  </si>
+  <si>
+    <t>払い出される薬剤が使用されることが想定された期間。</t>
+  </si>
+  <si>
+    <t>状況によっては、薬剤が供給される量として薬剤の錠数などの物理的量よりも、想定される供給期間を使って表現されることもある。たとえば、オーダされた量に基づいて薬剤を90日分提供するなど。可能であれば、量も示した方がより正確になる。ただし、実際には飲み忘れや紛失もあるためexpectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -2431,17 +2431,17 @@
   <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2450,27 +2450,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="178.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4187" uniqueCount="675">
   <si>
     <t>Property</t>
   </si>
@@ -912,6 +912,18 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:other</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>このリクエストの外部ID / External ids for this request</t>
+  </si>
+  <si>
+    <t>ビジネスプロセスによって定義されるこの薬物療法要求に関連付けられたidentifier、および/またはリソース自体への直接のURL参照が適切でない場合にそれを参照するために使用されるidentifier。これらは、パフォーマーまたは他のシステムによってこのリソースに割り当てられたビジネスidentifierであり、リソースが更新され、サーバーからサーバーに伝播するため、一定のままです。 / Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2428,7 +2440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO111"/>
+  <dimension ref="A1:AO112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -7997,39 +8009,41 @@
         <v>288</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8055,13 +8069,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8079,13 +8093,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>288</v>
+        <v>148</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8094,27 +8108,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>294</v>
+        <v>157</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>296</v>
+        <v>159</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>297</v>
+        <v>160</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8122,7 +8136,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>91</v>
@@ -8131,22 +8145,22 @@
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8172,13 +8186,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>301</v>
+        <v>186</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8196,10 +8210,10 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>91</v>
@@ -8211,16 +8225,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8228,10 +8242,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8239,7 +8253,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -8248,22 +8262,22 @@
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8289,13 +8303,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>186</v>
+        <v>305</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8313,10 +8327,10 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -8328,16 +8342,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8345,10 +8359,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8356,31 +8370,31 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8406,11 +8420,13 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8428,13 +8444,13 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8443,16 +8459,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8460,10 +8476,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8474,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8483,19 +8499,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8521,13 +8537,11 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8545,13 +8559,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8560,16 +8574,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8577,10 +8591,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8597,22 +8611,22 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>332</v>
+        <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8638,13 +8652,13 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>82</v>
@@ -8662,7 +8676,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8677,16 +8691,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8694,10 +8708,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8714,21 +8728,23 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8777,7 +8793,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8798,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8809,10 +8825,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8820,7 +8836,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8835,7 +8851,7 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>193</v>
+        <v>342</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>343</v>
@@ -8843,9 +8859,7 @@
       <c r="M55" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>345</v>
-      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8870,13 +8884,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8894,10 +8908,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8909,27 +8923,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8952,16 +8966,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>354</v>
+        <v>193</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8987,13 +9001,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9011,7 +9025,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9026,27 +9040,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9054,7 +9068,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
@@ -9066,19 +9080,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9128,10 +9142,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -9143,27 +9157,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9174,7 +9188,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9186,16 +9200,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9245,13 +9259,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9260,27 +9274,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9288,10 +9302,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9300,18 +9314,20 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9360,13 +9376,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9375,27 +9391,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9403,7 +9419,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
@@ -9418,17 +9434,15 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9477,7 +9491,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9492,27 +9506,27 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9532,19 +9546,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9594,7 +9608,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9609,16 +9623,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9626,10 +9640,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9649,19 +9663,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>193</v>
+        <v>399</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9687,11 +9701,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9709,7 +9725,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9724,16 +9740,16 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9741,10 +9757,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9764,19 +9780,19 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>409</v>
+        <v>193</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9802,13 +9818,11 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9826,7 +9840,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9841,16 +9855,16 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9858,10 +9872,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9872,7 +9886,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9884,16 +9898,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>193</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>416</v>
-      </c>
       <c r="N64" t="s" s="2">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9919,13 +9933,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9943,13 +9957,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9958,27 +9972,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10001,16 +10015,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>426</v>
+        <v>193</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10036,13 +10050,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10060,7 +10074,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10075,27 +10089,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>295</v>
+        <v>425</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10115,19 +10129,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10177,7 +10191,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10192,16 +10206,16 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10209,10 +10223,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10235,16 +10249,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>437</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10294,7 +10308,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10309,13 +10323,13 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10326,10 +10340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10352,16 +10366,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>443</v>
+        <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10411,7 +10425,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10426,13 +10440,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10443,10 +10457,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10457,7 +10471,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10469,18 +10483,18 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>447</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M69" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>451</v>
-      </c>
+      <c r="N69" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10528,13 +10542,13 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
@@ -10543,13 +10557,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10560,10 +10574,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10583,21 +10597,21 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10621,13 +10635,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>458</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10645,7 +10659,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10660,13 +10674,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10677,10 +10691,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10691,7 +10705,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10703,16 +10717,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>462</v>
+        <v>193</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>376</v>
+        <v>461</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10738,13 +10752,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>463</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10762,13 +10776,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10777,13 +10791,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10794,10 +10808,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10820,16 +10834,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>470</v>
-      </c>
       <c r="N72" t="s" s="2">
-        <v>471</v>
+        <v>380</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10879,7 +10893,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10894,13 +10908,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10911,10 +10925,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10937,16 +10951,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10996,7 +11010,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11011,13 +11025,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11028,10 +11042,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11042,7 +11056,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11054,15 +11068,17 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L74" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11111,13 +11127,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11126,13 +11142,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11143,10 +11159,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11169,13 +11185,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>169</v>
+        <v>487</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11226,7 +11242,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>486</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11238,16 +11254,16 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>173</v>
+        <v>491</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11258,10 +11274,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11272,7 +11288,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11284,13 +11300,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11329,29 +11345,31 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AC76" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11360,7 +11378,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11371,14 +11389,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" t="s" s="2">
         <v>495</v>
       </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11399,13 +11415,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11444,16 +11460,14 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>179</v>
@@ -11465,7 +11479,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11488,13 +11502,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11504,7 +11518,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11516,13 +11530,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11582,7 +11596,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11605,33 +11619,35 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="B79" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>137</v>
+        <v>506</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>507</v>
@@ -11639,12 +11655,8 @@
       <c r="M79" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N79" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11692,7 +11704,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>509</v>
+        <v>179</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11701,7 +11713,7 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>142</v>
@@ -11713,7 +11725,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11724,33 +11736,33 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>137</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>511</v>
@@ -11759,9 +11771,11 @@
         <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11809,19 +11823,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11830,7 +11844,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>514</v>
+        <v>134</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11841,10 +11855,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11867,15 +11881,17 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>169</v>
+        <v>487</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>170</v>
+        <v>515</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11924,7 +11940,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>172</v>
+        <v>514</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11936,7 +11952,7 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11945,7 +11961,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>173</v>
+        <v>518</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11956,21 +11972,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -11982,17 +11998,15 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12041,19 +12055,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12073,14 +12087,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>506</v>
+        <v>136</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12093,26 +12107,24 @@
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>508</v>
+        <v>176</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12160,7 +12172,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>509</v>
+        <v>179</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12181,7 +12193,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12192,44 +12204,46 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>519</v>
+        <v>137</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12277,19 +12291,19 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12298,7 +12312,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>523</v>
+        <v>134</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12309,10 +12323,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12335,16 +12349,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12394,7 +12408,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12415,7 +12429,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12426,10 +12440,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12452,7 +12466,7 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>530</v>
@@ -12461,7 +12475,7 @@
         <v>531</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12511,7 +12525,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12532,7 +12546,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12543,10 +12557,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12569,20 +12583,18 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>223</v>
+        <v>529</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>536</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12630,7 +12642,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12648,10 +12660,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12662,10 +12674,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12688,16 +12700,20 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>169</v>
+        <v>223</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>170</v>
+        <v>537</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12745,7 +12761,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>172</v>
+        <v>536</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12757,16 +12773,16 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>173</v>
+        <v>542</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12777,21 +12793,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12803,17 +12819,15 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12850,31 +12864,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12894,21 +12908,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -12917,19 +12931,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>380</v>
+        <v>137</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>542</v>
+        <v>138</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>543</v>
+        <v>176</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>544</v>
+        <v>140</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12967,31 +12981,31 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>545</v>
+        <v>179</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13000,21 +13014,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>547</v>
+        <v>173</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13037,24 +13051,22 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13098,7 +13110,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13107,7 +13119,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13119,21 +13131,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13153,25 +13165,27 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>558</v>
+        <v>384</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q92" s="2"/>
+      <c r="Q92" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="R92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13215,7 +13229,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13224,7 +13238,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -13233,24 +13247,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13273,16 +13287,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>519</v>
+        <v>562</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13332,7 +13346,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13350,24 +13364,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13390,16 +13404,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13449,7 +13463,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13467,24 +13481,24 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13507,15 +13521,17 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>169</v>
+        <v>529</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>170</v>
+        <v>577</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13564,7 +13580,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>172</v>
+        <v>576</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13576,16 +13592,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>580</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>173</v>
+        <v>581</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13596,21 +13612,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13622,17 +13638,15 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13669,31 +13683,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13713,21 +13727,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13736,23 +13750,21 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>581</v>
+        <v>137</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>582</v>
+        <v>138</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>583</v>
+        <v>176</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13788,31 +13800,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>586</v>
+        <v>179</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13821,21 +13833,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>587</v>
+        <v>173</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>588</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13852,74 +13864,74 @@
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>111</v>
+        <v>585</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="R98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13940,21 +13952,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13971,30 +13983,32 @@
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q99" s="2"/>
+      <c r="Q99" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="R99" t="s" s="2">
-        <v>603</v>
+        <v>82</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14012,13 +14026,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>82</v>
+        <v>598</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14036,7 +14050,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14057,21 +14071,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14094,24 +14108,24 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14153,7 +14167,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14162,7 +14176,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14174,21 +14188,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14211,26 +14225,24 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14272,7 +14284,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14281,7 +14293,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>82</v>
+        <v>617</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>103</v>
@@ -14293,21 +14305,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14327,27 +14339,29 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>624</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>82</v>
+        <v>624</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>82</v>
@@ -14389,7 +14403,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14410,21 +14424,21 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14447,7 +14461,7 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>483</v>
+        <v>628</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>629</v>
@@ -14455,7 +14469,9 @@
       <c r="M103" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N103" s="2"/>
+      <c r="N103" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14504,7 +14520,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14522,13 +14538,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="AM103" t="s" s="2">
-        <v>632</v>
-      </c>
       <c r="AN103" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14536,10 +14552,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14562,13 +14578,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>169</v>
+        <v>487</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>170</v>
+        <v>633</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>171</v>
+        <v>634</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14619,7 +14635,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>172</v>
+        <v>632</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14631,16 +14647,16 @@
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>173</v>
+        <v>636</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14651,21 +14667,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14677,17 +14693,15 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14736,19 +14750,19 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -14768,14 +14782,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>506</v>
+        <v>136</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14788,26 +14802,24 @@
         <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>507</v>
+        <v>138</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>508</v>
+        <v>176</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O106" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -14855,7 +14867,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>509</v>
+        <v>179</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14876,7 +14888,7 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
@@ -14887,44 +14899,46 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>629</v>
+        <v>511</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>637</v>
+        <v>512</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -14948,11 +14962,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>639</v>
+        <v>82</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14970,42 +14986,42 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>636</v>
+        <v>513</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>631</v>
+        <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>640</v>
+        <v>134</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>641</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15013,7 +15029,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>91</v>
@@ -15031,13 +15047,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15063,13 +15079,11 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15087,10 +15101,10 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>91</v>
@@ -15105,24 +15119,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15145,16 +15159,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>652</v>
+        <v>193</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>376</v>
+        <v>649</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15180,13 +15194,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15204,7 +15218,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15219,38 +15233,38 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>82</v>
+        <v>654</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>658</v>
+        <v>82</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15262,16 +15276,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>662</v>
+        <v>380</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15321,13 +15335,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15336,13 +15350,13 @@
         <v>103</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>82</v>
+        <v>659</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>82</v>
+        <v>652</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15353,14 +15367,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>662</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15379,16 +15393,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15438,7 +15452,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15453,18 +15467,135 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K112" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
+      <c r="L112" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO111" t="s" s="2">
+      <c r="M112" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4187" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="671">
   <si>
     <t>Property</t>
   </si>
@@ -912,18 +912,6 @@
   </si>
   <si>
     <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:other</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>このリクエストの外部ID / External ids for this request</t>
-  </si>
-  <si>
-    <t>ビジネスプロセスによって定義されるこの薬物療法要求に関連付けられたidentifier、および/またはリソース自体への直接のURL参照が適切でない場合にそれを参照するために使用されるidentifier。これらは、パフォーマーまたは他のシステムによってこのリソースに割り当てられたビジネスidentifierであり、リソースが更新され、サーバーからサーバーに伝播するため、一定のままです。 / Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -2440,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO112"/>
+  <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -8009,41 +7997,39 @@
         <v>288</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8069,13 +8055,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>292</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8093,13 +8079,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -8108,27 +8094,27 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>157</v>
+        <v>294</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>158</v>
+        <v>295</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>159</v>
+        <v>296</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>160</v>
+        <v>297</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>161</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8136,7 +8122,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>91</v>
@@ -8145,22 +8131,22 @@
         <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8186,13 +8172,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>186</v>
+        <v>301</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8210,10 +8196,10 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>91</v>
@@ -8225,16 +8211,16 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8242,10 +8228,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8253,7 +8239,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>91</v>
@@ -8262,22 +8248,22 @@
         <v>82</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8303,34 +8289,34 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>305</v>
+        <v>186</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>91</v>
@@ -8342,16 +8328,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8359,10 +8345,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8370,31 +8356,31 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8420,37 +8406,35 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AA51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AG51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
@@ -8459,16 +8443,16 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8476,10 +8460,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8490,7 +8474,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8499,19 +8483,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8537,11 +8521,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8559,13 +8545,13 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
@@ -8574,16 +8560,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8591,10 +8577,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8611,22 +8597,22 @@
         <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>111</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8652,31 +8638,31 @@
         <v>82</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8691,16 +8677,16 @@
         <v>103</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8708,10 +8694,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8728,23 +8714,21 @@
         <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8793,7 +8777,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8814,7 +8798,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8825,10 +8809,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8836,7 +8820,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8851,7 +8835,7 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>342</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>343</v>
@@ -8859,7 +8843,9 @@
       <c r="M55" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N55" s="2"/>
+      <c r="N55" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8884,13 +8870,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8908,10 +8894,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8923,27 +8909,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8966,16 +8952,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>193</v>
+        <v>354</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9001,13 +8987,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9025,7 +9011,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9040,27 +9026,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9068,7 +9054,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
@@ -9080,19 +9066,19 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9142,10 +9128,10 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>91</v>
@@ -9157,27 +9143,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>363</v>
+        <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9188,7 +9174,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9200,16 +9186,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9259,13 +9245,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9274,27 +9260,27 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9302,10 +9288,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9314,20 +9300,18 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9376,13 +9360,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9391,27 +9375,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9419,7 +9403,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
@@ -9434,15 +9418,17 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9491,7 +9477,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9506,27 +9492,27 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9546,19 +9532,19 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9608,7 +9594,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9623,16 +9609,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9640,10 +9626,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9663,19 +9649,19 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>399</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9701,13 +9687,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9725,7 +9709,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9740,16 +9724,16 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9757,10 +9741,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9780,19 +9764,19 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>193</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9818,11 +9802,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -9840,7 +9826,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9855,16 +9841,16 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9872,10 +9858,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9886,7 +9872,7 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
@@ -9898,16 +9884,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>413</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9933,13 +9919,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9957,13 +9943,13 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
@@ -9972,27 +9958,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10015,16 +10001,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>193</v>
+        <v>426</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10050,13 +10036,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10074,7 +10060,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10089,27 +10075,27 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>425</v>
+        <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10129,19 +10115,19 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10191,7 +10177,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10206,16 +10192,16 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10223,10 +10209,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10249,16 +10235,16 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>437</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10308,7 +10294,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10323,13 +10309,13 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10340,10 +10326,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10366,16 +10352,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>445</v>
+        <v>376</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10425,7 +10411,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10440,13 +10426,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10457,10 +10443,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10471,7 +10457,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10483,18 +10469,18 @@
         <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>447</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10542,13 +10528,13 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
@@ -10557,13 +10543,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10574,10 +10560,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10597,21 +10583,21 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10635,13 +10621,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10659,7 +10645,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10674,13 +10660,13 @@
         <v>103</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10691,10 +10677,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10705,7 +10691,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10717,16 +10703,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>193</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>461</v>
+        <v>376</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10752,13 +10738,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>462</v>
+        <v>82</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10776,13 +10762,13 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
@@ -10791,13 +10777,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10808,10 +10794,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10834,16 +10820,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10893,7 +10879,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10908,13 +10894,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10925,10 +10911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10951,16 +10937,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11010,7 +10996,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11025,13 +11011,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11042,10 +11028,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11056,7 +11042,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11068,17 +11054,15 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11127,13 +11111,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11142,13 +11126,13 @@
         <v>103</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11159,10 +11143,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11185,13 +11169,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>487</v>
+        <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11242,7 +11226,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>486</v>
+        <v>172</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11254,16 +11238,16 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>491</v>
+        <v>173</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11274,10 +11258,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11288,7 +11272,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11300,13 +11284,13 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11345,31 +11329,29 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11378,7 +11360,7 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>82</v>
@@ -11389,12 +11371,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11415,13 +11399,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>137</v>
+        <v>496</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11460,14 +11444,16 @@
         <v>82</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="AC77" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>179</v>
@@ -11479,7 +11465,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>82</v>
+        <v>499</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11502,13 +11488,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11518,7 +11504,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11530,13 +11516,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11596,7 +11582,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11619,35 +11605,33 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C79" t="s" s="2">
         <v>505</v>
       </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>506</v>
+        <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>507</v>
@@ -11655,8 +11639,12 @@
       <c r="M79" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11704,7 +11692,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>179</v>
+        <v>509</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11713,7 +11701,7 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>142</v>
@@ -11725,7 +11713,7 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>82</v>
@@ -11736,33 +11724,33 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>511</v>
@@ -11771,11 +11759,9 @@
         <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>513</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -11823,19 +11809,19 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -11844,7 +11830,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>134</v>
+        <v>514</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11855,10 +11841,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11881,17 +11867,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>487</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>515</v>
+        <v>170</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11940,7 +11924,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>514</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11952,7 +11936,7 @@
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -11961,7 +11945,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>518</v>
+        <v>173</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11972,21 +11956,21 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -11998,15 +11982,17 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12055,19 +12041,19 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12087,14 +12073,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>136</v>
+        <v>506</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12107,24 +12093,26 @@
         <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>138</v>
+        <v>507</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>176</v>
+        <v>508</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12172,7 +12160,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>179</v>
+        <v>509</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12193,7 +12181,7 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>82</v>
@@ -12204,46 +12192,44 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>137</v>
+        <v>519</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12291,19 +12277,19 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12312,7 +12298,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>134</v>
+        <v>523</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12323,10 +12309,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12349,16 +12335,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12408,7 +12394,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12429,7 +12415,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12440,10 +12426,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12466,7 +12452,7 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>530</v>
@@ -12475,7 +12461,7 @@
         <v>531</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12525,7 +12511,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12546,7 +12532,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12557,10 +12543,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12583,18 +12569,20 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>529</v>
+        <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="N87" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12642,7 +12630,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12660,10 +12648,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12674,10 +12662,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12700,20 +12688,16 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>537</v>
+        <v>170</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12761,7 +12745,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>536</v>
+        <v>172</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12773,16 +12757,16 @@
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>541</v>
+        <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>542</v>
+        <v>173</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12793,21 +12777,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12819,15 +12803,17 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -12864,31 +12850,31 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -12908,21 +12894,21 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -12931,19 +12917,19 @@
         <v>82</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>137</v>
+        <v>380</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>138</v>
+        <v>542</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>176</v>
+        <v>543</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>140</v>
+        <v>544</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12981,31 +12967,31 @@
         <v>82</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>179</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13014,21 +13000,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>173</v>
+        <v>547</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13051,22 +13037,24 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13110,7 +13098,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13119,7 +13107,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13131,21 +13119,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13165,72 +13153,70 @@
         <v>82</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>384</v>
+        <v>558</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q92" t="s" s="2">
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF92" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="R92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
@@ -13238,7 +13224,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>550</v>
+        <v>82</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
@@ -13247,24 +13233,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13287,16 +13273,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>562</v>
+        <v>519</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13346,7 +13332,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13364,24 +13350,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13404,16 +13390,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13463,7 +13449,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13481,24 +13467,24 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13521,17 +13507,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>529</v>
+        <v>169</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>577</v>
+        <v>170</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13580,7 +13564,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>576</v>
+        <v>172</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13592,16 +13576,16 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>581</v>
+        <v>173</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13612,21 +13596,21 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13638,15 +13622,17 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
@@ -13683,31 +13669,31 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -13727,21 +13713,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -13750,21 +13736,23 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>137</v>
+        <v>581</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>138</v>
+        <v>582</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>176</v>
+        <v>583</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>585</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -13800,31 +13788,31 @@
         <v>82</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>179</v>
+        <v>586</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -13833,21 +13821,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>173</v>
+        <v>587</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13864,30 +13852,30 @@
         <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J98" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>585</v>
+        <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
       </c>
@@ -13907,13 +13895,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13931,7 +13919,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13952,21 +13940,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13983,32 +13971,30 @@
         <v>82</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q99" t="s" s="2">
-        <v>597</v>
-      </c>
+      <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>82</v>
+        <v>603</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14026,13 +14012,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>598</v>
+        <v>82</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14050,7 +14036,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14071,21 +14057,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14108,24 +14094,24 @@
         <v>92</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>169</v>
+        <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14167,7 +14153,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14176,7 +14162,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14188,21 +14174,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14225,24 +14211,26 @@
         <v>92</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14284,7 +14272,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14293,7 +14281,7 @@
         <v>91</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>103</v>
@@ -14305,21 +14293,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14339,29 +14327,27 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>111</v>
+        <v>624</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>82</v>
@@ -14403,7 +14389,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14424,21 +14410,21 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14461,7 +14447,7 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>628</v>
+        <v>483</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>629</v>
@@ -14469,9 +14455,7 @@
       <c r="M103" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>380</v>
-      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14520,7 +14504,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14538,13 +14522,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14552,10 +14536,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14578,13 +14562,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>487</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>633</v>
+        <v>170</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>634</v>
+        <v>171</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14635,7 +14619,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>632</v>
+        <v>172</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14647,16 +14631,16 @@
         <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>636</v>
+        <v>173</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14667,21 +14651,21 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -14693,15 +14677,17 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -14750,19 +14736,19 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>82</v>
@@ -14782,14 +14768,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>136</v>
+        <v>506</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14802,24 +14788,26 @@
         <v>82</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>138</v>
+        <v>507</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>176</v>
+        <v>508</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -14867,7 +14855,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>179</v>
+        <v>509</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14888,7 +14876,7 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>82</v>
@@ -14899,46 +14887,44 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>511</v>
+        <v>629</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>512</v>
+        <v>637</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
       </c>
@@ -14962,13 +14948,11 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>82</v>
+        <v>639</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14986,42 +14970,42 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>513</v>
+        <v>636</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>82</v>
+        <v>631</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>134</v>
+        <v>640</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>82</v>
+        <v>641</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15029,7 +15013,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>91</v>
@@ -15047,13 +15031,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15079,11 +15063,13 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y108" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="Z108" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15101,10 +15087,10 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>91</v>
@@ -15119,24 +15105,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15159,16 +15145,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>193</v>
+        <v>652</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>649</v>
+        <v>376</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15194,31 +15180,31 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="Z109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>646</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15233,38 +15219,38 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>654</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>82</v>
@@ -15276,16 +15262,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>380</v>
+        <v>662</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15335,13 +15321,13 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
@@ -15350,13 +15336,13 @@
         <v>103</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>659</v>
+        <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>652</v>
+        <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15367,14 +15353,14 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>662</v>
+        <v>82</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15393,16 +15379,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15452,7 +15438,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15467,135 +15453,18 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -742,7 +742,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1200,7 +1200,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1469,7 +1469,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2066,7 +2066,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -2039,19 +2039,16 @@
     <t>MedicationRequest.substitution.reason</t>
   </si>
   <si>
-    <t>代替品を提供した（あるいは、しなかった）理由</t>
-  </si>
-  <si>
-    <t>代替品にしなければならなかった、あるいは代替品が認められなかった理由を示す。</t>
+    <t>後発医薬品への変更不可理由</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】後発医薬品への変更不可の理由を示す。令和6年保険改訂により、長期収載医薬品の変更不可を指定する場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
   </si>
   <si>
     <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
-    <t>別の薬物療法が処方されたものから置き換える（またはすべきではない）理由を説明するコード化された概念。 / A coded concept describing the reason that a different medication should (or should not) be substituted from what was prescribed.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>
   </si>
   <si>
     <t>not mapped</t>
@@ -2455,7 +2452,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -15063,13 +15060,11 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="Y108" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y108" s="2"/>
+      <c r="Z108" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15105,24 +15100,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>650</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15145,13 +15140,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>376</v>
@@ -15204,7 +15199,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15219,13 +15214,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>656</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15236,14 +15231,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15262,16 +15257,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>662</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15321,7 +15316,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15342,7 +15337,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15353,10 +15348,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15379,16 +15374,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15438,7 +15433,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15453,13 +15448,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4147" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -1032,9 +1032,6 @@
   </si>
   <si>
     <t>このMedicationRequestオーダの優先度。他のオーダと比較して表現される。</t>
-  </si>
-  <si>
-    <t>FHIRでは文字列の大きさが1MBを超えてはならない(SHALL NOT)。</t>
   </si>
   <si>
     <t>リクエストの実行に割り当てられる重要性のレベルを特定します。 / Identifies the level of importance to be assigned to actioning the request.</t>
@@ -8491,9 +8488,7 @@
       <c r="M52" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N52" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8521,10 +8516,10 @@
         <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8557,16 +8552,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8574,10 +8569,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8600,16 +8595,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8659,7 +8654,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8680,7 +8675,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8691,10 +8686,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8717,13 +8712,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8774,7 +8769,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8795,7 +8790,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8835,13 +8830,13 @@
         <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8870,11 +8865,11 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8891,7 +8886,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8906,27 +8901,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8949,16 +8944,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9008,7 +9003,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9023,27 +9018,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9066,16 +9061,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9125,7 +9120,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9140,27 +9135,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9183,16 +9178,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9242,7 +9237,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9257,16 +9252,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>378</v>
-      </c>
       <c r="AN58" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9274,10 +9269,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9300,13 +9295,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9357,7 +9352,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9372,27 +9367,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9415,16 +9410,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="N60" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9474,7 +9469,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9489,16 +9484,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9506,10 +9501,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9532,16 +9527,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="N61" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9591,7 +9586,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9606,16 +9601,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9623,10 +9618,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9652,13 +9647,13 @@
         <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9688,7 +9683,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9706,7 +9701,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9721,13 +9716,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9738,10 +9733,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9764,16 +9759,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="N63" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9823,7 +9818,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9844,10 +9839,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9855,10 +9850,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9884,13 +9879,13 @@
         <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9919,11 +9914,11 @@
         <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9940,7 +9935,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9955,27 +9950,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9998,16 +9993,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10057,7 +10052,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10072,16 +10067,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10089,10 +10084,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10115,16 +10110,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10174,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10189,13 +10184,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10206,10 +10201,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10235,13 +10230,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10291,7 +10286,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10312,7 +10307,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10323,10 +10318,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10349,16 +10344,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N68" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10408,7 +10403,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10423,13 +10418,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10440,10 +10435,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10469,14 +10464,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10525,7 +10520,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10540,13 +10535,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10557,10 +10552,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10586,13 +10581,13 @@
         <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10621,11 +10616,11 @@
         <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10642,7 +10637,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10663,7 +10658,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10674,10 +10669,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10700,16 +10695,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="N71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10759,7 +10754,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10774,13 +10769,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10791,10 +10786,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10817,16 +10812,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10876,7 +10871,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10891,13 +10886,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AM72" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10908,10 +10903,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10934,16 +10929,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10993,7 +10988,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11008,13 +11003,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11025,10 +11020,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11051,13 +11046,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11108,7 +11103,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11126,10 +11121,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11140,10 +11135,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11169,10 +11164,10 @@
         <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11255,10 +11250,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11284,10 +11279,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11368,13 +11363,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11396,13 +11391,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11462,7 +11457,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11485,13 +11480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C78" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11513,13 +11508,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11579,7 +11574,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11602,14 +11597,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11631,10 +11626,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11689,7 +11684,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11721,10 +11716,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11747,16 +11742,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11806,7 +11801,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11827,7 +11822,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11838,10 +11833,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11953,10 +11948,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12070,14 +12065,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12099,10 +12094,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12157,7 +12152,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12189,10 +12184,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12215,16 +12210,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>521</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>522</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12274,7 +12269,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12295,7 +12290,7 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
@@ -12306,10 +12301,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12332,16 +12327,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M85" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="N85" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12391,7 +12386,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12412,7 +12407,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12423,10 +12418,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12449,16 +12444,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>531</v>
-      </c>
       <c r="N86" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12508,7 +12503,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12529,7 +12524,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12540,10 +12535,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12569,16 +12564,16 @@
         <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N87" t="s" s="2">
+      <c r="O87" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12627,7 +12622,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12645,10 +12640,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12659,10 +12654,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12774,10 +12769,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12891,10 +12886,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12917,16 +12912,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12976,16 +12971,16 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI90" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12997,21 +12992,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13034,69 +13029,69 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="R91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="R91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>554</v>
-      </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13104,7 +13099,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13116,21 +13111,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13153,16 +13148,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="M92" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13212,7 +13207,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13230,24 +13225,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13270,16 +13265,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13329,7 +13324,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13347,24 +13342,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13387,16 +13382,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>575</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13446,7 +13441,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13464,10 +13459,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13478,10 +13473,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,10 +13588,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13710,10 +13705,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13736,19 +13731,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L97" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="L97" t="s" s="2">
+      <c r="M97" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13797,7 +13792,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13818,21 +13813,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13858,20 +13853,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q98" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13895,28 +13890,28 @@
         <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="Z98" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="Z98" t="s" s="2">
+      <c r="AA98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF98" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13937,21 +13932,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>598</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13977,63 +13972,63 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14054,21 +14049,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>606</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14094,72 +14089,72 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI100" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14171,21 +14166,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14211,65 +14206,65 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14290,21 +14285,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14327,16 +14322,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="M102" t="s" s="2">
-        <v>626</v>
-      </c>
       <c r="N102" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14386,7 +14381,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14407,10 +14402,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14418,10 +14413,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14444,13 +14439,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>630</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14501,7 +14496,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14519,10 +14514,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AM103" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14533,10 +14528,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14648,10 +14643,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14765,14 +14760,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14794,10 +14789,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14852,7 +14847,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14884,10 +14879,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14913,13 +14908,13 @@
         <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>637</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14949,7 +14944,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14967,7 +14962,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14985,24 +14980,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO107" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>641</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15028,13 +15023,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15064,7 +15059,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15082,7 +15077,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15100,24 +15095,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO108" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>649</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15140,16 +15135,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="L109" t="s" s="2">
         <v>651</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15199,7 +15194,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15214,13 +15209,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15231,14 +15226,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15257,16 +15252,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>661</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15316,7 +15311,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15337,7 +15332,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15348,10 +15343,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15374,16 +15369,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15433,7 +15428,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15448,13 +15443,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM111" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>669</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -2042,7 +2042,7 @@
     <t>【JP Core仕様】後発医薬品への変更不可の理由を示す。令和6年保険改訂により、長期収載医薬品の変更不可を指定する場合は「医療上の必要性がある」または「患者希望による」のいずれかを指定する。</t>
   </si>
   <si>
-    <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
+    <t>代替品の理由を表す一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationSubstitutionProhibitionReason_VS</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -1783,10 +1783,10 @@
     <t>許可されたリフィル回数</t>
   </si>
   <si>
-    <t>リフィル回数を示す整数である。患者が処方された薬を最初の払い出しから追加で受け取ることができる回数である。使用上の注意：この整数には最初の払い出しが含まれない。オーダが「30錠に加えて3回リフィル可」であれば、このオーダで合計で最大4回、120錠が患者に受け渡される。この数字を0とすることで，処方者がリフィルを許可しないということを明示することができる。</t>
-  </si>
-  <si>
-    <t>許可された払い出し回数は，最大でこの数字に1を足したものである。</t>
+    <t>リフィル回数を示す整数である。患者が処方された薬を最初の払い出しから追加で受け取ることができる回数である。使用上の注意：この整数には最初の払い出しが含まれない。オーダが「30錠に加えて3回リフィル可」であれば、このオーダで合計で最大4回、120錠が患者に受け渡される。この数字を0とすることで、処方者がリフィルを許可しないということを明示することができる。</t>
+  </si>
+  <si>
+    <t>許可された払い出し回数は、最大でこの数字に1を足したものである。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-medicationrequest.xlsx
@@ -491,7 +491,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
@@ -1504,7 +1504,7 @@
     <t>他の属性では伝えることができなかったMedicationRequestについての付加的情報。</t>
   </si>
   <si>
-    <t>構造化されたアノテーションが内システムでは、作成者や記録時間のない一つのアノテーションで情報を伝達している。このエレメントに情報の修正を要する可能性があるためにナラティブな情報も必要としている。Annotationsには機械処理が可能で修正される（"modifying")情報を伝達することに使うべきではない(SHOULD NOT)。これがSHOULDである理由はユーザの行動を強制することはほぼ不可能であるからである。</t>
+    <t>構造化されたアノテーションが内システムでは、作成者や記録時間のない一つのアノテーションで情報を伝達している。このエレメントに情報の修正を要する可能性があるためにナラティブな情報も必要としている。Annotationsには機械処理が可能で修正される（"modifying")情報を伝達することに使うべきではない(SHOULD NOT)。これがSHOULDである理由はユーザーの行動を強制することはほぼ不可能であるからである。</t>
   </si>
   <si>
     <t>Request.note</t>
@@ -2109,7 +2109,7 @@
     <t>ライフサイクルで関心のあるイベントのリスト</t>
   </si>
   <si>
-    <t>このリソースの現在のバージョンをユーザから見て関係していそうなキーとなる更新や状態遷移と識別される過去のバージョンのこのリソースあるいは調剤請求あるいはEvent ResourceについてのProvenance resourceへの参照。</t>
+    <t>このリソースの現在のバージョンをユーザーから見て関係していそうなキーとなる更新や状態遷移と識別される過去のバージョンのこのリソースあるいは調剤請求あるいはEvent ResourceについてのProvenance resourceへの参照。</t>
   </si>
   <si>
     <t>このエレメントには全てのバージョンのMedicationRequestについてのProvenanceが取り込まれているわけではない。「関連する」あるいは重要と思われたものだけである。現在のバージョンのResourceに関連したProvenance resourceを含めてはならない(SHALL NOT)。（もし、Provenanceとして「関連した」変化と思われれば、後の更新の一部として取り込まれる必要があるだろう。それまでは、このバージョンを_revincludeを使ってprovenanceとして指定して直接クエリーを発行することができる。全てのProvenanceがこのRequestについての履歴を対象として持つべきである。）</t>
